--- a/2026/GENERAL PAZ 138/Agosto/Agosto GRAL PAZ 138.xlsx
+++ b/2026/GENERAL PAZ 138/Agosto/Agosto GRAL PAZ 138.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD413AE0-CB6B-4650-A07B-F8152919C60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31D2140-E3B8-46C2-B7BB-BA664E1D8198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$101</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="105">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -303,9 +308,6 @@
     <t>Transf 12/06</t>
   </si>
   <si>
-    <t>VTO 17/08</t>
-  </si>
-  <si>
     <t>TRANSFERIR A  : Cuenta SANTANDER  533-033257/4 CBU :  0720533020000003325740 - CUIT: 30-71953248-5</t>
   </si>
   <si>
@@ -325,6 +327,24 @@
   </si>
   <si>
     <t>Transf 21/08</t>
+  </si>
+  <si>
+    <t>Se adeuda AGOSTO</t>
+  </si>
+  <si>
+    <t>Transf 31/07</t>
+  </si>
+  <si>
+    <t>Transf 18/08</t>
+  </si>
+  <si>
+    <t>Debito 20/08</t>
+  </si>
+  <si>
+    <t>LOS GASTOS COLOREADOS EN AMARILLO CORRESPONDEN A EGRESOS PROPIOS DE MESES ANTERIORES AL MES DE AGOSTO</t>
+  </si>
+  <si>
+    <t>VTO 17/09</t>
   </si>
 </sst>
 </file>
@@ -340,7 +360,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -618,6 +638,20 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1332,7 +1366,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1526,6 +1560,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="41" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="41" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="41" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="41" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="41" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1553,6 +1591,18 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1568,9 +1618,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1601,20 +1648,15 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="41" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="41" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="41" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="41" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="41" fillId="9" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="42" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -1724,9 +1766,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1764,9 +1806,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1799,9 +1841,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1834,9 +1893,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2010,17 +2086,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L93"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2039,75 +2115,75 @@
       <c r="C2" s="70"/>
       <c r="D2" s="70"/>
     </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1">
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
       <c r="A3" s="70"/>
       <c r="B3" s="70"/>
       <c r="C3" s="70"/>
       <c r="D3" s="70"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="145" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="145"/>
+      <c r="A4" s="149" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="149"/>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
     </row>
     <row r="5" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A5" s="145"/>
-      <c r="B5" s="145"/>
+      <c r="A5" s="149"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
     </row>
     <row r="6" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A6" s="145"/>
-      <c r="B6" s="145"/>
+      <c r="A6" s="149"/>
+      <c r="B6" s="149"/>
       <c r="C6" s="71"/>
       <c r="D6" s="71"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="145"/>
-      <c r="B7" s="145"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="149"/>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="153" t="s">
-        <v>92</v>
+      <c r="B9" s="157" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="153"/>
+      <c r="B10" s="157"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="153"/>
+      <c r="B11" s="157"/>
     </row>
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="152" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="148"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="148"/>
+      <c r="B14" s="152"/>
+      <c r="C14" s="152"/>
+      <c r="D14" s="152"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="148"/>
-      <c r="B15" s="148"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="148"/>
+      <c r="A15" s="152"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="152"/>
+      <c r="D15" s="152"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="148"/>
-      <c r="B16" s="148"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="148"/>
+      <c r="A16" s="152"/>
+      <c r="B16" s="152"/>
+      <c r="C16" s="152"/>
+      <c r="D16" s="152"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="148"/>
-      <c r="B17" s="148"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="148"/>
+      <c r="A17" s="152"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="152"/>
+      <c r="D17" s="152"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
       <c r="A18" s="60"/>
@@ -2115,13 +2191,13 @@
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
       <c r="A19" s="142"/>
       <c r="B19" s="60"/>
       <c r="C19" s="60"/>
       <c r="D19" s="60"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1">
       <c r="A20" s="60"/>
       <c r="B20" s="60"/>
       <c r="C20" s="60"/>
@@ -2222,41 +2298,49 @@
     </row>
     <row r="32" spans="1:7" ht="22.5" customHeight="1">
       <c r="A32" s="96" t="s">
-        <v>95</v>
-      </c>
-      <c r="B32" s="114"/>
-      <c r="C32" s="176">
+        <v>94</v>
+      </c>
+      <c r="B32" s="179" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="147">
         <v>130000</v>
       </c>
-      <c r="D32" s="81"/>
+      <c r="D32" s="81" t="s">
+        <v>100</v>
+      </c>
       <c r="F32" s="16"/>
       <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:7" ht="22.5" customHeight="1">
       <c r="A33" s="96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B33" s="114"/>
-      <c r="C33" s="177">
+      <c r="C33" s="148">
         <v>70000</v>
       </c>
-      <c r="D33" s="175"/>
+      <c r="D33" s="81" t="s">
+        <v>100</v>
+      </c>
       <c r="F33" s="16"/>
       <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:7" ht="22.5" customHeight="1">
       <c r="A34" s="96" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B34" s="114"/>
-      <c r="C34" s="177">
+      <c r="C34" s="148">
         <v>130000</v>
       </c>
-      <c r="D34" s="175"/>
+      <c r="D34" s="81" t="s">
+        <v>100</v>
+      </c>
       <c r="F34" s="16"/>
       <c r="G34" s="4"/>
     </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1">
+    <row r="35" spans="1:7" ht="15.75" thickBot="1">
       <c r="A35" s="9" t="s">
         <v>26</v>
       </c>
@@ -2276,60 +2360,62 @@
       <c r="D36" s="26"/>
     </row>
     <row r="37" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A37" s="146" t="s">
+      <c r="A37" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="147"/>
-      <c r="C37" s="173">
+      <c r="B37" s="151"/>
+      <c r="C37" s="145">
         <v>87914</v>
       </c>
       <c r="D37" s="80" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1">
-      <c r="A38" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A38" s="150" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="151"/>
+      <c r="C38" s="177">
+        <v>84333</v>
+      </c>
+      <c r="D38" s="178" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A39" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="50">
+      <c r="B39" s="9"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="50">
         <f>SUM(C37:C37)</f>
         <v>87914</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
-      <c r="A39" s="8" t="s">
+    <row r="40" spans="1:7" hidden="1">
+      <c r="A40" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B39" s="115"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="51"/>
-    </row>
-    <row r="40" spans="1:7" hidden="1">
-      <c r="A40" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" s="84"/>
-      <c r="D40" s="80"/>
-      <c r="F40" s="74"/>
+      <c r="B40" s="115"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="51"/>
     </row>
     <row r="41" spans="1:7" hidden="1">
       <c r="A41" s="46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B41" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="84"/>
       <c r="D41" s="80"/>
+      <c r="F41" s="74"/>
     </row>
     <row r="42" spans="1:7" hidden="1">
       <c r="A42" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B42" s="46" t="s">
         <v>74</v>
@@ -2339,308 +2425,314 @@
     </row>
     <row r="43" spans="1:7" hidden="1">
       <c r="A43" s="46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B43" s="46" t="s">
         <v>74</v>
       </c>
       <c r="C43" s="85"/>
-      <c r="D43" s="79"/>
-    </row>
-    <row r="44" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1">
-      <c r="A44" s="9" t="s">
+      <c r="D43" s="80"/>
+    </row>
+    <row r="44" spans="1:7" hidden="1">
+      <c r="A44" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="85"/>
+      <c r="D44" s="79"/>
+    </row>
+    <row r="45" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1">
+      <c r="A45" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B44" s="115"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="50">
-        <f>SUM(C40:C43)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="8" t="s">
+      <c r="B45" s="115"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="50">
+        <f>SUM(C41:C44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B45" s="115"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="51"/>
-    </row>
-    <row r="46" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A46" s="60" t="s">
+      <c r="B46" s="115"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="51"/>
+    </row>
+    <row r="47" spans="1:7" ht="14.25" customHeight="1">
+      <c r="A47" s="60" t="s">
         <v>82</v>
-      </c>
-      <c r="B46" s="46"/>
-      <c r="C46" s="144">
-        <v>37949.040000000001</v>
-      </c>
-      <c r="D46" s="78" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A47" s="46" t="s">
-        <v>80</v>
       </c>
       <c r="B47" s="46"/>
       <c r="C47" s="144">
-        <v>223478.44</v>
-      </c>
-      <c r="D47" s="78"/>
+        <v>81160.509999999995</v>
+      </c>
+      <c r="D47" s="78" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1">
       <c r="A48" s="46" t="s">
         <v>80</v>
       </c>
       <c r="B48" s="46"/>
-      <c r="C48" s="174">
+      <c r="C48" s="144">
+        <v>223478.44</v>
+      </c>
+      <c r="D48" s="78" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A49" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="46"/>
+      <c r="C49" s="146">
         <v>204474.88</v>
       </c>
-      <c r="D48" s="78" t="s">
+      <c r="D49" s="78" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1">
-      <c r="A49" s="9" t="s">
+    <row r="50" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A50" s="9" t="s">
         <v>3</v>
-      </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="50">
-        <f>SUM(C46:C48)</f>
-        <v>465902.36</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15" thickBot="1">
-      <c r="A50" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="13"/>
-      <c r="D50" s="53"/>
-    </row>
-    <row r="51" spans="1:6" ht="39.6" customHeight="1">
-      <c r="A51" s="146" t="s">
-        <v>98</v>
-      </c>
-      <c r="B51" s="147"/>
-      <c r="C51" s="174">
+      <c r="D50" s="50">
+        <f>SUM(C47:C49)</f>
+        <v>509113.83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A51" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="53"/>
+    </row>
+    <row r="52" spans="1:6" ht="39.6" customHeight="1">
+      <c r="A52" s="150" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" s="151"/>
+      <c r="C52" s="146">
         <v>102680</v>
       </c>
-      <c r="D51" s="76"/>
-    </row>
-    <row r="52" spans="1:6" ht="15" thickBot="1">
-      <c r="A52" s="9" t="s">
+      <c r="D52" s="76"/>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A53" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="55">
-        <f>SUM(C51:C51)</f>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="55">
+        <f>SUM(C52:C52)</f>
         <v>102680</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1">
-      <c r="A53" s="8" t="s">
+    <row r="54" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A54" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="116"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="53"/>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="46"/>
-      <c r="B54" s="46"/>
-      <c r="C54" s="87"/>
-      <c r="D54" s="56"/>
-    </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1">
-      <c r="A55" s="117" t="s">
+      <c r="B54" s="116"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="53"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="46"/>
+      <c r="B55" s="46"/>
+      <c r="C55" s="87"/>
+      <c r="D55" s="56"/>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A56" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="B55" s="117"/>
-      <c r="C55" s="57"/>
-      <c r="D55" s="50">
-        <f>SUM(C54:C54)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1">
-      <c r="A56" s="46"/>
-      <c r="B56" s="46"/>
-      <c r="C56" s="46"/>
-      <c r="D56" s="58"/>
-    </row>
-    <row r="57" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A57" s="150" t="s">
+      <c r="B56" s="117"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="50">
+        <f>SUM(C55:C55)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A57" s="46"/>
+      <c r="B57" s="46"/>
+      <c r="C57" s="46"/>
+      <c r="D57" s="58"/>
+    </row>
+    <row r="58" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A58" s="154" t="s">
         <v>75</v>
       </c>
-      <c r="B57" s="151"/>
-      <c r="C57" s="152"/>
-      <c r="D57" s="59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1">
-      <c r="A58" s="118"/>
-      <c r="B58" s="60"/>
-      <c r="C58" s="60"/>
-      <c r="D58" s="61"/>
-      <c r="E58" s="17"/>
-    </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1">
-      <c r="A59" s="119" t="s">
+      <c r="B58" s="155"/>
+      <c r="C58" s="156"/>
+      <c r="D58" s="59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A59" s="118"/>
+      <c r="B59" s="60"/>
+      <c r="C59" s="60"/>
+      <c r="D59" s="61"/>
+      <c r="E59" s="17"/>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A60" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="120"/>
-      <c r="C59" s="62"/>
-      <c r="D59" s="63">
-        <f>(SUM(D25:D57))</f>
-        <v>986496.36</v>
-      </c>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="60"/>
-      <c r="B60" s="60"/>
-      <c r="C60" s="60"/>
-      <c r="D60" s="60"/>
-      <c r="F60" s="75"/>
-    </row>
-    <row r="61" spans="1:6" ht="15" thickBot="1">
+      <c r="B60" s="120"/>
+      <c r="C60" s="62"/>
+      <c r="D60" s="63">
+        <f>(SUM(D25:D58))</f>
+        <v>1029707.8300000001</v>
+      </c>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="60"/>
       <c r="B61" s="60"/>
       <c r="C61" s="60"/>
       <c r="D61" s="60"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="121" t="s">
+      <c r="F61" s="75"/>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A62" s="60"/>
+      <c r="B62" s="60"/>
+      <c r="C62" s="60"/>
+      <c r="D62" s="60"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="B62" s="122"/>
-      <c r="C62" s="64"/>
-      <c r="D62" s="65"/>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="146"/>
-      <c r="B63" s="147"/>
-      <c r="C63" s="85"/>
-      <c r="D63" s="76"/>
+      <c r="B63" s="122"/>
+      <c r="C63" s="64"/>
+      <c r="D63" s="65"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="146"/>
-      <c r="B64" s="147"/>
+      <c r="A64" s="150"/>
+      <c r="B64" s="151"/>
       <c r="C64" s="85"/>
-      <c r="D64" s="52"/>
+      <c r="D64" s="76"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="125"/>
-      <c r="B65" s="126"/>
+      <c r="A65" s="150"/>
+      <c r="B65" s="151"/>
       <c r="C65" s="85"/>
       <c r="D65" s="52"/>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="127"/>
-      <c r="B66" s="128"/>
-      <c r="C66" s="129"/>
-      <c r="D66" s="129">
-        <f>SUM(C63:C65)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15" customHeight="1">
-      <c r="A67" s="60"/>
-      <c r="B67" s="60"/>
-      <c r="C67" s="60"/>
-      <c r="D67" s="60"/>
-    </row>
-    <row r="68" spans="1:4" hidden="1">
+      <c r="A66" s="125"/>
+      <c r="B66" s="126"/>
+      <c r="C66" s="85"/>
+      <c r="D66" s="52"/>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="127"/>
+      <c r="B67" s="128"/>
+      <c r="C67" s="129"/>
+      <c r="D67" s="129">
+        <f>SUM(C64:C66)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15" customHeight="1">
       <c r="A68" s="60"/>
       <c r="B68" s="60"/>
       <c r="C68" s="60"/>
       <c r="D68" s="60"/>
     </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="130" t="s">
+    <row r="69" spans="1:4" hidden="1">
+      <c r="A69" s="60"/>
+      <c r="B69" s="60"/>
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="B69" s="130"/>
-      <c r="C69" s="131"/>
-      <c r="D69" s="143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="15" thickBot="1">
-      <c r="A70" s="60"/>
-      <c r="B70" s="60"/>
-      <c r="C70" s="60"/>
-      <c r="D70" s="60"/>
-    </row>
-    <row r="71" spans="1:4" ht="15" thickBot="1">
-      <c r="A71" s="119" t="s">
+      <c r="B70" s="130"/>
+      <c r="C70" s="131"/>
+      <c r="D70" s="143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A71" s="60"/>
+      <c r="B71" s="60"/>
+      <c r="C71" s="60"/>
+      <c r="D71" s="60"/>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A72" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="B71" s="120"/>
-      <c r="C71" s="62"/>
-      <c r="D71" s="63">
-        <f>D66+D69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="15" thickBot="1">
-      <c r="A72" s="60"/>
-      <c r="B72" s="60"/>
-      <c r="C72" s="60"/>
-      <c r="D72" s="60"/>
-    </row>
-    <row r="73" spans="1:4" ht="15" thickBot="1">
-      <c r="A73" s="132" t="s">
+      <c r="B72" s="120"/>
+      <c r="C72" s="62"/>
+      <c r="D72" s="63">
+        <f>D67+D70</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A73" s="60"/>
+      <c r="B73" s="60"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A74" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="B73" s="133">
-        <f>D59</f>
-        <v>986496.36</v>
-      </c>
-      <c r="C73" s="134"/>
-      <c r="D73" s="60"/>
-    </row>
-    <row r="74" spans="1:4" ht="15" thickBot="1">
-      <c r="A74" s="132" t="s">
+      <c r="B74" s="133">
+        <f>D60</f>
+        <v>1029707.8300000001</v>
+      </c>
+      <c r="C74" s="134"/>
+      <c r="D74" s="60"/>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A75" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="B74" s="133">
-        <f>D59-D57</f>
-        <v>986496.36</v>
-      </c>
-      <c r="C74" s="60"/>
-      <c r="D74" s="60"/>
-    </row>
-    <row r="75" spans="1:4" ht="15" thickBot="1">
-      <c r="A75" s="132" t="s">
-        <v>34</v>
-      </c>
       <c r="B75" s="133">
-        <f>D71-D69</f>
-        <v>0</v>
+        <f>D60-D58</f>
+        <v>1029707.8300000001</v>
       </c>
       <c r="C75" s="60"/>
       <c r="D75" s="60"/>
     </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1">
+    <row r="76" spans="1:4" ht="15.75" thickBot="1">
       <c r="A76" s="132" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B76" s="133">
-        <f>D71</f>
+        <f>D72-D70</f>
         <v>0</v>
       </c>
       <c r="C76" s="60"/>
       <c r="D76" s="60"/>
     </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="60"/>
-      <c r="B77" s="60"/>
+    <row r="77" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A77" s="132" t="s">
+        <v>49</v>
+      </c>
+      <c r="B77" s="133">
+        <f>D72</f>
+        <v>0</v>
+      </c>
       <c r="C77" s="60"/>
       <c r="D77" s="60"/>
     </row>
@@ -2651,124 +2743,176 @@
       <c r="D78" s="60"/>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="60"/>
-      <c r="B79" s="60"/>
-      <c r="C79" s="60"/>
-      <c r="D79" s="60"/>
-    </row>
-    <row r="80" spans="1:4" ht="15" thickBot="1">
-      <c r="A80" s="135" t="s">
+      <c r="A79" s="181" t="s">
+        <v>103</v>
+      </c>
+      <c r="B79" s="181"/>
+      <c r="C79" s="181"/>
+      <c r="D79" s="181"/>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="181"/>
+      <c r="B80" s="181"/>
+      <c r="C80" s="181"/>
+      <c r="D80" s="181"/>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="181"/>
+      <c r="B81" s="181"/>
+      <c r="C81" s="181"/>
+      <c r="D81" s="181"/>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="181"/>
+      <c r="B82" s="181"/>
+      <c r="C82" s="181"/>
+      <c r="D82" s="181"/>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="181"/>
+      <c r="B83" s="181"/>
+      <c r="C83" s="181"/>
+      <c r="D83" s="181"/>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="181"/>
+      <c r="B84" s="181"/>
+      <c r="C84" s="181"/>
+      <c r="D84" s="181"/>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="60"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="60"/>
+      <c r="D85" s="60"/>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="60"/>
+      <c r="B86" s="60"/>
+      <c r="C86" s="60"/>
+      <c r="D86" s="60"/>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="60"/>
+      <c r="B87" s="60"/>
+      <c r="C87" s="60"/>
+      <c r="D87" s="60"/>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A88" s="135" t="s">
         <v>44</v>
       </c>
-      <c r="B80" s="136"/>
-      <c r="C80" s="60"/>
-      <c r="D80" s="60"/>
-    </row>
-    <row r="81" spans="1:12" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A81" s="7" t="s">
+      <c r="B88" s="136"/>
+      <c r="C88" s="60"/>
+      <c r="D88" s="60"/>
+    </row>
+    <row r="89" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A89" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B81" s="137">
-        <v>87629.729999999981</v>
-      </c>
-      <c r="C81" s="60"/>
-    </row>
-    <row r="82" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A82" s="138" t="s">
+      <c r="B89" s="137">
+        <v>87629.73</v>
+      </c>
+      <c r="C89" s="60"/>
+    </row>
+    <row r="90" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A90" s="138" t="s">
         <v>52</v>
       </c>
-      <c r="B82" s="54">
+      <c r="B90" s="54">
         <f>PRORRATEO!H18</f>
-        <v>951360.18000000017</v>
-      </c>
-      <c r="C82" s="60"/>
-    </row>
-    <row r="83" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A83" s="138" t="s">
+        <v>890688.32</v>
+      </c>
+      <c r="C90" s="60"/>
+    </row>
+    <row r="91" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A91" s="138" t="s">
         <v>51</v>
       </c>
-      <c r="B83" s="54">
-        <f>B92</f>
-        <v>0</v>
-      </c>
-      <c r="C83" s="60"/>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="A84" s="140" t="s">
+      <c r="B91" s="54">
+        <f>B100</f>
+        <v>0</v>
+      </c>
+      <c r="C91" s="60"/>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="B84" s="54">
-        <f>-B74</f>
-        <v>-986496.36</v>
-      </c>
-      <c r="C84" s="60"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="A85" s="139" t="s">
+      <c r="B92" s="54">
+        <f>-B75</f>
+        <v>-1029707.8300000001</v>
+      </c>
+      <c r="C92" s="60"/>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="139" t="s">
         <v>36</v>
       </c>
-      <c r="B85" s="54">
-        <f>-(B75)</f>
-        <v>0</v>
-      </c>
-      <c r="C85" s="60"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="A86" s="6" t="s">
+      <c r="B93" s="54">
+        <f>-(B76)</f>
+        <v>0</v>
+      </c>
+      <c r="C93" s="60"/>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B86" s="97">
-        <f>SUM(B81:B85)</f>
-        <v>52493.550000000163</v>
-      </c>
-      <c r="C86" s="124"/>
-    </row>
-    <row r="87" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B87" s="16"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="124"/>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="A88" s="149" t="s">
+      <c r="B94" s="97">
+        <f>SUM(B89:B93)</f>
+        <v>-51389.780000000144</v>
+      </c>
+      <c r="C94" s="124"/>
+    </row>
+    <row r="95" spans="1:4" ht="34.5" customHeight="1">
+      <c r="B95" s="16"/>
+      <c r="C95" s="17"/>
+      <c r="D95" s="124"/>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="B88" s="149"/>
-    </row>
-    <row r="89" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A89" s="149"/>
-      <c r="B89" s="149"/>
-    </row>
-    <row r="90" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A90" s="66"/>
-      <c r="B90" s="12"/>
-    </row>
-    <row r="91" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A91" s="66"/>
-      <c r="B91" s="12"/>
-    </row>
-    <row r="92" spans="1:12">
-      <c r="A92" s="18" t="s">
+      <c r="B96" s="153"/>
+    </row>
+    <row r="97" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A97" s="153"/>
+      <c r="B97" s="153"/>
+    </row>
+    <row r="98" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A98" s="66"/>
+      <c r="B98" s="12"/>
+    </row>
+    <row r="99" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A99" s="66"/>
+      <c r="B99" s="12"/>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B92" s="67">
-        <f>SUM(B90:B91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12">
-      <c r="L93" s="3"/>
+      <c r="B100" s="67">
+        <f>SUM(B98:B99)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="L101" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A88:B89"/>
+    <mergeCell ref="A96:B97"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A79:D84"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2779,45 +2923,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.9" customHeight="1">
+    <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="98"/>
-      <c r="B1" s="154" t="str">
+      <c r="B1" s="162" t="str">
         <f>RESUMEN!A4</f>
         <v>TRANSFERIR A  : Cuenta SANTANDER  533-033257/4 CBU :  0720533020000003325740 - CUIT: 30-71953248-5</v>
       </c>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="162"/>
+      <c r="K1" s="162"/>
       <c r="L1" s="99"/>
       <c r="M1" s="99"/>
       <c r="N1" s="99"/>
@@ -2826,16 +2970,16 @@
     </row>
     <row r="2" spans="1:21" ht="14.25" customHeight="1">
       <c r="A2" s="101"/>
-      <c r="B2" s="155"/>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
+      <c r="B2" s="163"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
       <c r="L2" s="102"/>
       <c r="M2" s="102" t="s">
         <v>4</v>
@@ -2852,16 +2996,16 @@
     </row>
     <row r="3" spans="1:21" ht="16.5" customHeight="1" thickBot="1">
       <c r="A3" s="104"/>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="164"/>
       <c r="L3" s="105"/>
       <c r="M3" s="105" t="s">
         <v>53</v>
@@ -2874,96 +3018,96 @@
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="168"/>
-      <c r="D4" s="168"/>
-      <c r="E4" s="168"/>
-      <c r="F4" s="168"/>
-      <c r="G4" s="168"/>
-      <c r="H4" s="168"/>
-      <c r="I4" s="168"/>
-      <c r="J4" s="168"/>
-      <c r="K4" s="168"/>
-      <c r="L4" s="168"/>
-      <c r="M4" s="168"/>
-      <c r="N4" s="168"/>
-      <c r="O4" s="168"/>
-      <c r="P4" s="169"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="175"/>
+      <c r="H4" s="175"/>
+      <c r="I4" s="175"/>
+      <c r="J4" s="175"/>
+      <c r="K4" s="175"/>
+      <c r="L4" s="175"/>
+      <c r="M4" s="175"/>
+      <c r="N4" s="175"/>
+      <c r="O4" s="175"/>
+      <c r="P4" s="176"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="170" t="s">
+      <c r="A5" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="172" t="s">
+      <c r="B5" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="159" t="s">
+      <c r="C5" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="159" t="s">
+      <c r="D5" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="159" t="s">
+      <c r="E5" s="161" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="159" t="s">
+      <c r="F5" s="161" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="159" t="s">
+      <c r="G5" s="161" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="159" t="s">
+      <c r="H5" s="161" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="159" t="s">
+      <c r="I5" s="161" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="163" t="s">
+      <c r="J5" s="170" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="161" t="s">
+      <c r="K5" s="168" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="161" t="s">
+      <c r="L5" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="161" t="s">
+      <c r="M5" s="168" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="165" t="s">
+      <c r="N5" s="172" t="s">
         <v>48</v>
       </c>
       <c r="O5" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="157" t="s">
+      <c r="P5" s="165" t="s">
         <v>46</v>
       </c>
       <c r="S5" s="17"/>
       <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="171"/>
-      <c r="B6" s="172"/>
-      <c r="C6" s="159"/>
-      <c r="D6" s="159"/>
-      <c r="E6" s="160"/>
-      <c r="F6" s="159"/>
-      <c r="G6" s="159"/>
-      <c r="H6" s="159"/>
-      <c r="I6" s="160"/>
-      <c r="J6" s="164"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="161"/>
-      <c r="M6" s="162"/>
-      <c r="N6" s="166"/>
+      <c r="A6" s="159"/>
+      <c r="B6" s="160"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="167"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
+      <c r="I6" s="167"/>
+      <c r="J6" s="171"/>
+      <c r="K6" s="169"/>
+      <c r="L6" s="168"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="173"/>
       <c r="O6" s="22" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 17/08</v>
-      </c>
-      <c r="P6" s="157"/>
+        <v>VTO 17/09</v>
+      </c>
+      <c r="P6" s="165"/>
       <c r="S6" s="16">
         <v>65160</v>
       </c>
@@ -2993,7 +3137,7 @@
         <v>11.2</v>
       </c>
       <c r="G7" s="29">
-        <v>1335136.01</v>
+        <v>1487190.01</v>
       </c>
       <c r="H7" s="29">
         <v>0</v>
@@ -3001,11 +3145,11 @@
       <c r="I7" s="30"/>
       <c r="J7" s="91">
         <f>G7-H7</f>
-        <v>1335136.01</v>
+        <v>1487190.01</v>
       </c>
       <c r="K7" s="91">
         <f>IF(J7&gt;0,J7*3%,0)</f>
-        <v>40054.080300000001</v>
+        <v>44615.700299999997</v>
       </c>
       <c r="L7" s="141">
         <f>O$3*F7%</f>
@@ -3020,11 +3164,11 @@
       </c>
       <c r="O7" s="94">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>1487190.01</v>
+        <v>1643806.01</v>
       </c>
       <c r="P7" s="95">
         <f t="shared" ref="P7:P16" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>1531806.01</v>
+        <v>1693120.01</v>
       </c>
       <c r="Q7" s="17">
         <v>0.01</v>
@@ -3058,19 +3202,19 @@
         <v>11.2</v>
       </c>
       <c r="G8" s="28">
-        <v>643156.02</v>
+        <v>413951.02</v>
       </c>
       <c r="H8" s="29">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="I8" s="30"/>
       <c r="J8" s="31">
         <f t="shared" ref="J8:J16" si="2">G8-H8</f>
-        <v>293156.02</v>
+        <v>413951.02</v>
       </c>
       <c r="K8" s="31">
         <f t="shared" ref="K8:K16" si="3">IF(J8&gt;0,J8*3%,0)</f>
-        <v>8794.6805999999997</v>
+        <v>12418.5306</v>
       </c>
       <c r="L8" s="32">
         <f t="shared" ref="L8:L17" si="4">O$3*F8%</f>
@@ -3085,11 +3229,11 @@
       </c>
       <c r="O8" s="34">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>413951.02</v>
+        <v>538370.02</v>
       </c>
       <c r="P8" s="35">
         <f t="shared" si="0"/>
-        <v>426370.02</v>
+        <v>554521.02</v>
       </c>
       <c r="Q8" s="17">
         <f>Q7+0.01</f>
@@ -3125,19 +3269,19 @@
         <v>8.9</v>
       </c>
       <c r="G9" s="29">
-        <v>89000.03</v>
-      </c>
-      <c r="H9" s="29">
-        <v>0</v>
+        <v>180670.03</v>
+      </c>
+      <c r="H9" s="180">
+        <v>187000</v>
       </c>
       <c r="I9" s="30"/>
       <c r="J9" s="91">
         <f t="shared" si="2"/>
-        <v>89000.03</v>
+        <v>-6329.9700000000012</v>
       </c>
       <c r="K9" s="31">
         <f t="shared" si="3"/>
-        <v>2670.0009</v>
+        <v>0</v>
       </c>
       <c r="L9" s="92">
         <f t="shared" si="4"/>
@@ -3152,11 +3296,11 @@
       </c>
       <c r="O9" s="94">
         <f t="shared" ref="O9:O16" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>180670.03</v>
+        <v>82670.03</v>
       </c>
       <c r="P9" s="95">
         <f t="shared" si="0"/>
-        <v>186090.03</v>
+        <v>85150.03</v>
       </c>
       <c r="Q9" s="17">
         <f t="shared" ref="Q9:Q16" si="7">Q8+0.01</f>
@@ -3191,19 +3335,19 @@
         <v>8.9</v>
       </c>
       <c r="G10" s="28">
-        <v>91643.04</v>
+        <v>91722.04</v>
       </c>
       <c r="H10" s="29">
-        <v>89000</v>
+        <v>0</v>
       </c>
       <c r="I10" s="30"/>
       <c r="J10" s="31">
         <f t="shared" si="2"/>
-        <v>2643.0399999999936</v>
+        <v>91722.04</v>
       </c>
       <c r="K10" s="31">
         <f t="shared" si="3"/>
-        <v>79.291199999999805</v>
+        <v>2751.6611999999996</v>
       </c>
       <c r="L10" s="32">
         <f t="shared" si="4"/>
@@ -3218,11 +3362,11 @@
       </c>
       <c r="O10" s="34">
         <f t="shared" si="6"/>
-        <v>91722.04</v>
+        <v>183474.04</v>
       </c>
       <c r="P10" s="35">
         <f t="shared" si="0"/>
-        <v>94474.04</v>
+        <v>188978.04</v>
       </c>
       <c r="Q10" s="17">
         <f t="shared" si="7"/>
@@ -3259,14 +3403,13 @@
       <c r="G11" s="28">
         <v>98000.05</v>
       </c>
-      <c r="H11" s="29">
-        <f>G11</f>
-        <v>98000.05</v>
+      <c r="H11" s="180">
+        <v>98100</v>
       </c>
       <c r="I11" s="30"/>
       <c r="J11" s="31">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-99.94999999999709</v>
       </c>
       <c r="K11" s="31">
         <f t="shared" si="3"/>
@@ -3285,11 +3428,11 @@
       </c>
       <c r="O11" s="34">
         <f t="shared" si="6"/>
-        <v>98000.05</v>
+        <v>97900.05</v>
       </c>
       <c r="P11" s="35">
         <f t="shared" si="0"/>
-        <v>100940.05</v>
+        <v>100837.05</v>
       </c>
       <c r="Q11" s="17">
         <f t="shared" si="7"/>
@@ -3326,7 +3469,7 @@
       <c r="G12" s="28">
         <v>98000.06</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="180">
         <f>G12</f>
         <v>98000.06</v>
       </c>
@@ -3393,14 +3536,13 @@
       <c r="G13" s="28">
         <v>89000.07</v>
       </c>
-      <c r="H13" s="29">
-        <f>G13</f>
-        <v>89000.07</v>
+      <c r="H13" s="180">
+        <v>91670.07</v>
       </c>
       <c r="I13" s="30"/>
       <c r="J13" s="31">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-2670</v>
       </c>
       <c r="K13" s="31">
         <f t="shared" si="3"/>
@@ -3419,11 +3561,11 @@
       </c>
       <c r="O13" s="34">
         <f t="shared" si="6"/>
-        <v>89000.07</v>
+        <v>86330.07</v>
       </c>
       <c r="P13" s="35">
         <f t="shared" si="0"/>
-        <v>91670.07</v>
+        <v>88920.07</v>
       </c>
       <c r="Q13" s="17">
         <f t="shared" si="7"/>
@@ -3461,19 +3603,19 @@
         <v>8.9</v>
       </c>
       <c r="G14" s="28">
-        <v>88159.08</v>
-      </c>
-      <c r="H14" s="29">
-        <v>0</v>
+        <v>185198.07999999999</v>
+      </c>
+      <c r="H14" s="180">
+        <v>185198</v>
       </c>
       <c r="I14" s="30"/>
       <c r="J14" s="31">
         <f t="shared" si="2"/>
-        <v>88159.08</v>
+        <v>7.9999999987194315E-2</v>
       </c>
       <c r="K14" s="31">
         <f t="shared" si="3"/>
-        <v>2644.7723999999998</v>
+        <v>2.3999999996158292E-3</v>
       </c>
       <c r="L14" s="32">
         <f t="shared" si="4"/>
@@ -3488,11 +3630,11 @@
       </c>
       <c r="O14" s="34">
         <f t="shared" si="6"/>
-        <v>179804.08</v>
+        <v>89000.08</v>
       </c>
       <c r="P14" s="35">
         <f t="shared" si="0"/>
-        <v>185198.07999999999</v>
+        <v>91670.080000000002</v>
       </c>
       <c r="Q14" s="17">
         <f t="shared" si="7"/>
@@ -3529,15 +3671,15 @@
         <v>11.2</v>
       </c>
       <c r="G15" s="29">
+        <v>112000.09</v>
+      </c>
+      <c r="H15" s="180">
         <v>115360.09</v>
-      </c>
-      <c r="H15" s="29">
-        <v>115360</v>
       </c>
       <c r="I15" s="30"/>
       <c r="J15" s="91">
         <f t="shared" si="2"/>
-        <v>8.999999999650754E-2</v>
+        <v>-3360</v>
       </c>
       <c r="K15" s="91">
         <v>0</v>
@@ -3555,11 +3697,11 @@
       </c>
       <c r="O15" s="94">
         <f t="shared" si="6"/>
-        <v>112000.09</v>
+        <v>108640.09</v>
       </c>
       <c r="P15" s="95">
         <f t="shared" si="0"/>
-        <v>115360.09</v>
+        <v>111899.09</v>
       </c>
       <c r="Q15" s="17">
         <f t="shared" si="7"/>
@@ -3576,7 +3718,7 @@
         <v>141245</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="16.2" customHeight="1">
+    <row r="16" spans="1:21" ht="16.149999999999999" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -3596,17 +3738,17 @@
       <c r="G16" s="28">
         <v>112000.1</v>
       </c>
-      <c r="H16" s="29">
-        <v>112000</v>
+      <c r="H16" s="180">
+        <v>115360.1</v>
       </c>
       <c r="I16" s="30"/>
       <c r="J16" s="31">
         <f t="shared" si="2"/>
-        <v>0.10000000000582077</v>
+        <v>-3360</v>
       </c>
       <c r="K16" s="31">
         <f t="shared" si="3"/>
-        <v>3.000000000174623E-3</v>
+        <v>0</v>
       </c>
       <c r="L16" s="32">
         <f t="shared" si="4"/>
@@ -3621,11 +3763,11 @@
       </c>
       <c r="O16" s="34">
         <f t="shared" si="6"/>
-        <v>112000.1</v>
+        <v>108640.1</v>
       </c>
       <c r="P16" s="35">
         <f t="shared" si="0"/>
-        <v>115360.1</v>
+        <v>111899.1</v>
       </c>
       <c r="Q16" s="17">
         <f t="shared" si="7"/>
@@ -3642,7 +3784,7 @@
         <v>243540</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15" thickBot="1">
+    <row r="17" spans="1:17" ht="15.75" thickBot="1">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -3676,7 +3818,7 @@
       <c r="P17" s="35"/>
       <c r="Q17" s="17"/>
     </row>
-    <row r="18" spans="1:17" ht="15" thickBot="1">
+    <row r="18" spans="1:17" ht="15.75" thickBot="1">
       <c r="B18" s="41"/>
       <c r="C18" s="42"/>
       <c r="D18" s="43"/>
@@ -3687,11 +3829,11 @@
       </c>
       <c r="G18" s="20">
         <f>SUM(G7:G17)</f>
-        <v>2759454.55</v>
-      </c>
-      <c r="H18" s="23">
+        <v>2867731.55</v>
+      </c>
+      <c r="H18" s="20">
         <f>SUM(H7:H17)</f>
-        <v>951360.18000000017</v>
+        <v>890688.32</v>
       </c>
       <c r="I18" s="23">
         <f>SUM(I7:I17)</f>
@@ -3713,11 +3855,11 @@
       </c>
       <c r="O18" s="45">
         <f>SUM(O7:O16)</f>
-        <v>2862337.55</v>
+        <v>3036830.55</v>
       </c>
       <c r="P18" s="45">
         <f>SUM(P7:P16)</f>
-        <v>2948208.55</v>
+        <v>3127934.55</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -3725,98 +3867,93 @@
       <c r="E19" s="19"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="D21" s="158" t="s">
+      <c r="D21" s="166" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="158"/>
-      <c r="F21" s="158"/>
-      <c r="G21" s="158"/>
-      <c r="H21" s="158"/>
-      <c r="I21" s="158"/>
-      <c r="J21" s="158"/>
-      <c r="K21" s="158"/>
-      <c r="L21" s="158"/>
-      <c r="M21" s="158"/>
-      <c r="N21" s="158"/>
-      <c r="O21" s="158"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="166"/>
+      <c r="G21" s="166"/>
+      <c r="H21" s="166"/>
+      <c r="I21" s="166"/>
+      <c r="J21" s="166"/>
+      <c r="K21" s="166"/>
+      <c r="L21" s="166"/>
+      <c r="M21" s="166"/>
+      <c r="N21" s="166"/>
+      <c r="O21" s="166"/>
     </row>
     <row r="22" spans="1:17">
-      <c r="D22" s="158"/>
-      <c r="E22" s="158"/>
-      <c r="F22" s="158"/>
-      <c r="G22" s="158"/>
-      <c r="H22" s="158"/>
-      <c r="I22" s="158"/>
-      <c r="J22" s="158"/>
-      <c r="K22" s="158"/>
-      <c r="L22" s="158"/>
-      <c r="M22" s="158"/>
-      <c r="N22" s="158"/>
-      <c r="O22" s="158"/>
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="166"/>
+      <c r="H22" s="166"/>
+      <c r="I22" s="166"/>
+      <c r="J22" s="166"/>
+      <c r="K22" s="166"/>
+      <c r="L22" s="166"/>
+      <c r="M22" s="166"/>
+      <c r="N22" s="166"/>
+      <c r="O22" s="166"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="D23" s="158"/>
-      <c r="E23" s="158"/>
-      <c r="F23" s="158"/>
-      <c r="G23" s="158"/>
-      <c r="H23" s="158"/>
-      <c r="I23" s="158"/>
-      <c r="J23" s="158"/>
-      <c r="K23" s="158"/>
-      <c r="L23" s="158"/>
-      <c r="M23" s="158"/>
-      <c r="N23" s="158"/>
-      <c r="O23" s="158"/>
+      <c r="D23" s="166"/>
+      <c r="E23" s="166"/>
+      <c r="F23" s="166"/>
+      <c r="G23" s="166"/>
+      <c r="H23" s="166"/>
+      <c r="I23" s="166"/>
+      <c r="J23" s="166"/>
+      <c r="K23" s="166"/>
+      <c r="L23" s="166"/>
+      <c r="M23" s="166"/>
+      <c r="N23" s="166"/>
+      <c r="O23" s="166"/>
     </row>
     <row r="24" spans="1:17">
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
-      <c r="F24" s="158"/>
-      <c r="G24" s="158"/>
-      <c r="H24" s="158"/>
-      <c r="I24" s="158"/>
-      <c r="J24" s="158"/>
-      <c r="K24" s="158"/>
-      <c r="L24" s="158"/>
-      <c r="M24" s="158"/>
-      <c r="N24" s="158"/>
-      <c r="O24" s="158"/>
+      <c r="D24" s="166"/>
+      <c r="E24" s="166"/>
+      <c r="F24" s="166"/>
+      <c r="G24" s="166"/>
+      <c r="H24" s="166"/>
+      <c r="I24" s="166"/>
+      <c r="J24" s="166"/>
+      <c r="K24" s="166"/>
+      <c r="L24" s="166"/>
+      <c r="M24" s="166"/>
+      <c r="N24" s="166"/>
+      <c r="O24" s="166"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="158"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="158"/>
-      <c r="J25" s="158"/>
-      <c r="K25" s="158"/>
-      <c r="L25" s="158"/>
-      <c r="M25" s="158"/>
-      <c r="N25" s="158"/>
-      <c r="O25" s="158"/>
+      <c r="D25" s="166"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="166"/>
+      <c r="G25" s="166"/>
+      <c r="H25" s="166"/>
+      <c r="I25" s="166"/>
+      <c r="J25" s="166"/>
+      <c r="K25" s="166"/>
+      <c r="L25" s="166"/>
+      <c r="M25" s="166"/>
+      <c r="N25" s="166"/>
+      <c r="O25" s="166"/>
     </row>
     <row r="26" spans="1:17" ht="65.25" customHeight="1">
-      <c r="D26" s="158"/>
-      <c r="E26" s="158"/>
-      <c r="F26" s="158"/>
-      <c r="G26" s="158"/>
-      <c r="H26" s="158"/>
-      <c r="I26" s="158"/>
-      <c r="J26" s="158"/>
-      <c r="K26" s="158"/>
-      <c r="L26" s="158"/>
-      <c r="M26" s="158"/>
-      <c r="N26" s="158"/>
-      <c r="O26" s="158"/>
+      <c r="D26" s="166"/>
+      <c r="E26" s="166"/>
+      <c r="F26" s="166"/>
+      <c r="G26" s="166"/>
+      <c r="H26" s="166"/>
+      <c r="I26" s="166"/>
+      <c r="J26" s="166"/>
+      <c r="K26" s="166"/>
+      <c r="L26" s="166"/>
+      <c r="M26" s="166"/>
+      <c r="N26" s="166"/>
+      <c r="O26" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D21:O26"/>
@@ -3830,6 +3967,11 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>

--- a/2026/GENERAL PAZ 138/Agosto/Agosto GRAL PAZ 138.xlsx
+++ b/2026/GENERAL PAZ 138/Agosto/Agosto GRAL PAZ 138.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31D2140-E3B8-46C2-B7BB-BA664E1D8198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31280EF-45F5-4834-957B-063CE6A7EADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -107,9 +107,6 @@
     <t>GASTOS ORDINARIOS SIN PREVISION:</t>
   </si>
   <si>
-    <t>Saldo anterior</t>
-  </si>
-  <si>
     <t xml:space="preserve">TOTAL </t>
   </si>
   <si>
@@ -345,6 +342,12 @@
   </si>
   <si>
     <t>VTO 17/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gastos bancarios </t>
+  </si>
+  <si>
+    <t>Saldo anterior -  A fin de Junio del 2026</t>
   </si>
 </sst>
 </file>
@@ -360,7 +363,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,20 +634,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1366,7 +1355,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1374,7 +1363,6 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1559,103 +1547,104 @@
     <xf numFmtId="44" fontId="8" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="41" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="41" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="41" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="41" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="41" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="41" fillId="9" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="42" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -2100,187 +2089,187 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="73" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="69"/>
+      <c r="A1" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="68"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="70" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
+      <c r="A2" s="69" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
     </row>
     <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="149" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" s="149"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
+      <c r="A4" s="145" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="145"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
     </row>
     <row r="5" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A5" s="149"/>
-      <c r="B5" s="149"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
+      <c r="A5" s="145"/>
+      <c r="B5" s="145"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
     </row>
     <row r="6" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A6" s="149"/>
-      <c r="B6" s="149"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
+      <c r="A6" s="145"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="149"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
+      <c r="A7" s="145"/>
+      <c r="B7" s="145"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="157" t="s">
-        <v>104</v>
+      <c r="B9" s="153" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="157"/>
+      <c r="B10" s="153"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="157"/>
+      <c r="B11" s="153"/>
     </row>
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="152" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="152"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
+      <c r="A14" s="148" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="148"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="148"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="152"/>
-      <c r="B15" s="152"/>
-      <c r="C15" s="152"/>
-      <c r="D15" s="152"/>
+      <c r="A15" s="148"/>
+      <c r="B15" s="148"/>
+      <c r="C15" s="148"/>
+      <c r="D15" s="148"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="152"/>
-      <c r="B16" s="152"/>
-      <c r="C16" s="152"/>
-      <c r="D16" s="152"/>
+      <c r="A16" s="148"/>
+      <c r="B16" s="148"/>
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="152"/>
-      <c r="B17" s="152"/>
-      <c r="C17" s="152"/>
-      <c r="D17" s="152"/>
+      <c r="A17" s="148"/>
+      <c r="B17" s="148"/>
+      <c r="C17" s="148"/>
+      <c r="D17" s="148"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A18" s="60"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
-      <c r="A19" s="142"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
+      <c r="A19" s="141"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1">
-      <c r="A20" s="60"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
+      <c r="A20" s="59"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="121" t="s">
+      <c r="A21" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="122"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="65"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="64"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="G22" s="16"/>
+      <c r="A22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="G22" s="15"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A23" s="46"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="111">
-        <v>0</v>
-      </c>
-      <c r="D23" s="46"/>
+      <c r="A23" s="45"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="110">
+        <v>0</v>
+      </c>
+      <c r="D23" s="45"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="112" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="112"/>
-      <c r="C24" s="68">
+      <c r="A24" s="111" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="111"/>
+      <c r="C24" s="67">
         <f>SUM(C23:C23)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="47"/>
+      <c r="D24" s="46"/>
     </row>
     <row r="25" spans="1:7" ht="0.6" customHeight="1">
-      <c r="A25" s="46"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="72"/>
+      <c r="A25" s="45"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="71"/>
     </row>
     <row r="26" spans="1:7" hidden="1">
-      <c r="A26" s="46"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="72"/>
+      <c r="A26" s="45"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="71"/>
     </row>
     <row r="27" spans="1:7" hidden="1">
-      <c r="A27" s="46"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="72"/>
+      <c r="A27" s="45"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="71"/>
     </row>
     <row r="28" spans="1:7" hidden="1">
-      <c r="A28" s="46"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="72"/>
+      <c r="A28" s="45"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="71"/>
     </row>
     <row r="29" spans="1:7" hidden="1">
-      <c r="A29" s="112" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="113"/>
-      <c r="C29" s="21">
+      <c r="A29" s="111" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="112"/>
+      <c r="C29" s="20">
         <f>SUM(C25:C28)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="47"/>
+      <c r="D29" s="46"/>
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A30" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="9"/>
+      <c r="A30" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="8"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="48">
+      <c r="D30" s="47">
         <f>C24+C29</f>
         <v>0</v>
       </c>
@@ -2288,611 +2277,616 @@
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="49"/>
+      <c r="A31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="48"/>
       <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A32" s="96" t="s">
+      <c r="A32" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="144" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="174">
+        <v>130000</v>
+      </c>
+      <c r="D32" s="80" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="15"/>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A33" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="179" t="s">
+      <c r="B33" s="113"/>
+      <c r="C33" s="175">
+        <v>70000</v>
+      </c>
+      <c r="D33" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="147">
+      <c r="F33" s="15"/>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A34" s="95" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="113"/>
+      <c r="C34" s="175">
         <v>130000</v>
       </c>
-      <c r="D32" s="81" t="s">
-        <v>100</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="4"/>
-    </row>
-    <row r="33" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A33" s="96" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="114"/>
-      <c r="C33" s="148">
-        <v>70000</v>
-      </c>
-      <c r="D33" s="81" t="s">
-        <v>100</v>
-      </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="4"/>
-    </row>
-    <row r="34" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A34" s="96" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="114"/>
-      <c r="C34" s="148">
-        <v>130000</v>
-      </c>
-      <c r="D34" s="81" t="s">
-        <v>100</v>
-      </c>
-      <c r="F34" s="16"/>
+      <c r="D34" s="80" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" s="15"/>
       <c r="G34" s="4"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="48">
+      <c r="A35" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="47">
         <f>SUM(C32:C34)</f>
         <v>330000</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A36" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="26"/>
+      <c r="A36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="25"/>
     </row>
     <row r="37" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A37" s="150" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" s="151"/>
-      <c r="C37" s="145">
+      <c r="A37" s="146" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" s="147"/>
+      <c r="C37" s="176">
         <v>87914</v>
       </c>
-      <c r="D37" s="80" t="s">
-        <v>93</v>
+      <c r="D37" s="79" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A38" s="150" t="s">
-        <v>90</v>
-      </c>
-      <c r="B38" s="151"/>
+      <c r="A38" s="146" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="147"/>
       <c r="C38" s="177">
         <v>84333</v>
       </c>
-      <c r="D38" s="178" t="s">
-        <v>102</v>
+      <c r="D38" s="143" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="50">
+      <c r="B39" s="8"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="49">
         <f>SUM(C37:C37)</f>
         <v>87914</v>
       </c>
     </row>
     <row r="40" spans="1:7" hidden="1">
-      <c r="A40" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="115"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="51"/>
+      <c r="A40" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="114"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="50"/>
     </row>
     <row r="41" spans="1:7" hidden="1">
-      <c r="A41" s="46" t="s">
+      <c r="A41" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="83"/>
+      <c r="D41" s="79"/>
+      <c r="F41" s="73"/>
+    </row>
+    <row r="42" spans="1:7" hidden="1">
+      <c r="A42" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="B41" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" s="84"/>
-      <c r="D41" s="80"/>
-      <c r="F41" s="74"/>
-    </row>
-    <row r="42" spans="1:7" hidden="1">
-      <c r="A42" s="46" t="s">
+      <c r="B42" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="84"/>
+      <c r="D42" s="79"/>
+    </row>
+    <row r="43" spans="1:7" hidden="1">
+      <c r="A43" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" s="85"/>
-      <c r="D42" s="80"/>
-    </row>
-    <row r="43" spans="1:7" hidden="1">
-      <c r="A43" s="46" t="s">
+      <c r="B43" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="84"/>
+      <c r="D43" s="79"/>
+    </row>
+    <row r="44" spans="1:7" hidden="1">
+      <c r="A44" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" s="85"/>
-      <c r="D43" s="80"/>
-    </row>
-    <row r="44" spans="1:7" hidden="1">
-      <c r="A44" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" s="85"/>
-      <c r="D44" s="79"/>
+      <c r="B44" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="84"/>
+      <c r="D44" s="78"/>
     </row>
     <row r="45" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B45" s="115"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="50">
+      <c r="B45" s="114"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="49">
         <f>SUM(C41:C44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B46" s="115"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="51"/>
+      <c r="A46" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="114"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="50"/>
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A47" s="60" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="46"/>
-      <c r="C47" s="144">
+      <c r="A47" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="45"/>
+      <c r="C47" s="84">
         <v>81160.509999999995</v>
       </c>
-      <c r="D47" s="78" t="s">
-        <v>98</v>
+      <c r="D47" s="77" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A48" s="46" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" s="46"/>
-      <c r="C48" s="144">
+      <c r="A48" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="45"/>
+      <c r="C48" s="84">
         <v>223478.44</v>
       </c>
-      <c r="D48" s="78" t="s">
-        <v>101</v>
+      <c r="D48" s="77" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A49" s="46" t="s">
-        <v>80</v>
-      </c>
-      <c r="B49" s="46"/>
-      <c r="C49" s="146">
+      <c r="A49" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49" s="45"/>
+      <c r="C49" s="178">
         <v>204474.88</v>
       </c>
-      <c r="D49" s="78" t="s">
-        <v>91</v>
+      <c r="D49" s="77" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B50" s="9"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="50">
+      <c r="B50" s="8"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="49">
         <f>SUM(C47:C49)</f>
         <v>509113.83</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="53"/>
+      <c r="A51" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B51" s="8"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="52"/>
     </row>
     <row r="52" spans="1:6" ht="39.6" customHeight="1">
-      <c r="A52" s="150" t="s">
-        <v>97</v>
-      </c>
-      <c r="B52" s="151"/>
-      <c r="C52" s="146">
+      <c r="A52" s="146" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="147"/>
+      <c r="C52" s="178">
         <v>102680</v>
       </c>
-      <c r="D52" s="76"/>
+      <c r="D52" s="75"/>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="9" t="s">
+      <c r="A53" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="55">
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="54">
         <f>SUM(C52:C52)</f>
         <v>102680</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="116"/>
+      <c r="B54" s="115"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="53"/>
+      <c r="D54" s="52"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="46"/>
-      <c r="B55" s="46"/>
-      <c r="C55" s="87"/>
-      <c r="D55" s="56"/>
+      <c r="A55" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" s="45"/>
+      <c r="C55" s="86">
+        <v>8607.9599999999991</v>
+      </c>
+      <c r="D55" s="55"/>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="117" t="s">
-        <v>26</v>
-      </c>
-      <c r="B56" s="117"/>
-      <c r="C56" s="57"/>
-      <c r="D56" s="50">
+      <c r="A56" s="116" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" s="116"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="49">
         <f>SUM(C55:C55)</f>
-        <v>0</v>
+        <v>8607.9599999999991</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="46"/>
-      <c r="B57" s="46"/>
-      <c r="C57" s="46"/>
-      <c r="D57" s="58"/>
+      <c r="A57" s="45"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="57"/>
     </row>
     <row r="58" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A58" s="154" t="s">
-        <v>75</v>
-      </c>
-      <c r="B58" s="155"/>
-      <c r="C58" s="156"/>
-      <c r="D58" s="59">
-        <v>0</v>
+      <c r="A58" s="150" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58" s="151"/>
+      <c r="C58" s="152"/>
+      <c r="D58" s="58">
+        <f>1400000-1038315.79</f>
+        <v>361684.20999999996</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="118"/>
-      <c r="B59" s="60"/>
-      <c r="C59" s="60"/>
-      <c r="D59" s="61"/>
-      <c r="E59" s="17"/>
+      <c r="A59" s="117"/>
+      <c r="B59" s="59"/>
+      <c r="C59" s="59"/>
+      <c r="D59" s="60"/>
+      <c r="E59" s="16"/>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="119" t="s">
+      <c r="A60" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="B60" s="120"/>
-      <c r="C60" s="62"/>
-      <c r="D60" s="63">
+      <c r="B60" s="119"/>
+      <c r="C60" s="61"/>
+      <c r="D60" s="62">
         <f>(SUM(D25:D58))</f>
-        <v>1029707.8300000001</v>
-      </c>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
+        <v>1400000</v>
+      </c>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="60"/>
-      <c r="B61" s="60"/>
-      <c r="C61" s="60"/>
-      <c r="D61" s="60"/>
-      <c r="F61" s="75"/>
+      <c r="A61" s="59"/>
+      <c r="B61" s="59"/>
+      <c r="C61" s="59"/>
+      <c r="D61" s="59"/>
+      <c r="F61" s="74"/>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="60"/>
-      <c r="B62" s="60"/>
-      <c r="C62" s="60"/>
-      <c r="D62" s="60"/>
+      <c r="A62" s="59"/>
+      <c r="B62" s="59"/>
+      <c r="C62" s="59"/>
+      <c r="D62" s="59"/>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="121" t="s">
+      <c r="A63" s="120" t="s">
+        <v>30</v>
+      </c>
+      <c r="B63" s="121"/>
+      <c r="C63" s="63"/>
+      <c r="D63" s="64"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="146"/>
+      <c r="B64" s="147"/>
+      <c r="C64" s="84"/>
+      <c r="D64" s="75"/>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="146"/>
+      <c r="B65" s="147"/>
+      <c r="C65" s="84"/>
+      <c r="D65" s="51"/>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="124"/>
+      <c r="B66" s="125"/>
+      <c r="C66" s="84"/>
+      <c r="D66" s="51"/>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="126"/>
+      <c r="B67" s="127"/>
+      <c r="C67" s="128"/>
+      <c r="D67" s="128">
+        <f>SUM(C64:C66)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15" customHeight="1">
+      <c r="A68" s="59"/>
+      <c r="B68" s="59"/>
+      <c r="C68" s="59"/>
+      <c r="D68" s="59"/>
+    </row>
+    <row r="69" spans="1:4" hidden="1">
+      <c r="A69" s="59"/>
+      <c r="B69" s="59"/>
+      <c r="C69" s="59"/>
+      <c r="D69" s="59"/>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="B63" s="122"/>
-      <c r="C63" s="64"/>
-      <c r="D63" s="65"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="150"/>
-      <c r="B64" s="151"/>
-      <c r="C64" s="85"/>
-      <c r="D64" s="76"/>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="150"/>
-      <c r="B65" s="151"/>
-      <c r="C65" s="85"/>
-      <c r="D65" s="52"/>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="125"/>
-      <c r="B66" s="126"/>
-      <c r="C66" s="85"/>
-      <c r="D66" s="52"/>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="127"/>
-      <c r="B67" s="128"/>
-      <c r="C67" s="129"/>
-      <c r="D67" s="129">
-        <f>SUM(C64:C66)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15" customHeight="1">
-      <c r="A68" s="60"/>
-      <c r="B68" s="60"/>
-      <c r="C68" s="60"/>
-      <c r="D68" s="60"/>
-    </row>
-    <row r="69" spans="1:4" hidden="1">
-      <c r="A69" s="60"/>
-      <c r="B69" s="60"/>
-      <c r="C69" s="60"/>
-      <c r="D69" s="60"/>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="130" t="s">
+      <c r="B70" s="129"/>
+      <c r="C70" s="130"/>
+      <c r="D70" s="142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A71" s="59"/>
+      <c r="B71" s="59"/>
+      <c r="C71" s="59"/>
+      <c r="D71" s="59"/>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A72" s="118" t="s">
         <v>32</v>
       </c>
-      <c r="B70" s="130"/>
-      <c r="C70" s="131"/>
-      <c r="D70" s="143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A71" s="60"/>
-      <c r="B71" s="60"/>
-      <c r="C71" s="60"/>
-      <c r="D71" s="60"/>
-    </row>
-    <row r="72" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A72" s="119" t="s">
+      <c r="B72" s="119"/>
+      <c r="C72" s="61"/>
+      <c r="D72" s="62">
+        <f>D67+D70</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A73" s="59"/>
+      <c r="B73" s="59"/>
+      <c r="C73" s="59"/>
+      <c r="D73" s="59"/>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A74" s="131" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" s="132">
+        <f>D60</f>
+        <v>1400000</v>
+      </c>
+      <c r="C74" s="133"/>
+      <c r="D74" s="59"/>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A75" s="131" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75" s="132">
+        <f>D60-D58</f>
+        <v>1038315.79</v>
+      </c>
+      <c r="C75" s="59"/>
+      <c r="D75" s="59"/>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A76" s="131" t="s">
         <v>33</v>
       </c>
-      <c r="B72" s="120"/>
-      <c r="C72" s="62"/>
-      <c r="D72" s="63">
-        <f>D67+D70</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A73" s="60"/>
-      <c r="B73" s="60"/>
-      <c r="C73" s="60"/>
-      <c r="D73" s="60"/>
-    </row>
-    <row r="74" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A74" s="132" t="s">
-        <v>23</v>
-      </c>
-      <c r="B74" s="133">
-        <f>D60</f>
-        <v>1029707.8300000001</v>
-      </c>
-      <c r="C74" s="134"/>
-      <c r="D74" s="60"/>
-    </row>
-    <row r="75" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A75" s="132" t="s">
-        <v>24</v>
-      </c>
-      <c r="B75" s="133">
-        <f>D60-D58</f>
-        <v>1029707.8300000001</v>
-      </c>
-      <c r="C75" s="60"/>
-      <c r="D75" s="60"/>
-    </row>
-    <row r="76" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A76" s="132" t="s">
+      <c r="B76" s="132">
+        <f>D72-D70</f>
+        <v>0</v>
+      </c>
+      <c r="C76" s="59"/>
+      <c r="D76" s="59"/>
+    </row>
+    <row r="77" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A77" s="131" t="s">
+        <v>48</v>
+      </c>
+      <c r="B77" s="132">
+        <f>D72</f>
+        <v>0</v>
+      </c>
+      <c r="C77" s="59"/>
+      <c r="D77" s="59"/>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="59"/>
+      <c r="B78" s="59"/>
+      <c r="C78" s="59"/>
+      <c r="D78" s="59"/>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="154" t="s">
+        <v>102</v>
+      </c>
+      <c r="B79" s="154"/>
+      <c r="C79" s="154"/>
+      <c r="D79" s="154"/>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="154"/>
+      <c r="B80" s="154"/>
+      <c r="C80" s="154"/>
+      <c r="D80" s="154"/>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="154"/>
+      <c r="B81" s="154"/>
+      <c r="C81" s="154"/>
+      <c r="D81" s="154"/>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="154"/>
+      <c r="B82" s="154"/>
+      <c r="C82" s="154"/>
+      <c r="D82" s="154"/>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="154"/>
+      <c r="B83" s="154"/>
+      <c r="C83" s="154"/>
+      <c r="D83" s="154"/>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="154"/>
+      <c r="B84" s="154"/>
+      <c r="C84" s="154"/>
+      <c r="D84" s="154"/>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="59"/>
+      <c r="B85" s="59"/>
+      <c r="C85" s="59"/>
+      <c r="D85" s="59"/>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="59"/>
+      <c r="B86" s="59"/>
+      <c r="C86" s="59"/>
+      <c r="D86" s="59"/>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="59"/>
+      <c r="B87" s="59"/>
+      <c r="C87" s="59"/>
+      <c r="D87" s="59"/>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A88" s="134" t="s">
+        <v>43</v>
+      </c>
+      <c r="B88" s="135"/>
+      <c r="C88" s="59"/>
+      <c r="D88" s="59"/>
+    </row>
+    <row r="89" spans="1:4" ht="21.75" customHeight="1" thickBot="1">
+      <c r="A89" s="179" t="s">
+        <v>105</v>
+      </c>
+      <c r="B89" s="136">
+        <v>-167155.70999999996</v>
+      </c>
+      <c r="C89" s="59"/>
+    </row>
+    <row r="90" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A90" s="137" t="s">
+        <v>51</v>
+      </c>
+      <c r="B90" s="53">
+        <f>PRORRATEO!H18</f>
+        <v>985688.32</v>
+      </c>
+      <c r="C90" s="59"/>
+    </row>
+    <row r="91" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A91" s="137" t="s">
+        <v>50</v>
+      </c>
+      <c r="B91" s="53">
+        <f>B100</f>
+        <v>0</v>
+      </c>
+      <c r="C91" s="59"/>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="139" t="s">
         <v>34</v>
       </c>
-      <c r="B76" s="133">
-        <f>D72-D70</f>
-        <v>0</v>
-      </c>
-      <c r="C76" s="60"/>
-      <c r="D76" s="60"/>
-    </row>
-    <row r="77" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A77" s="132" t="s">
-        <v>49</v>
-      </c>
-      <c r="B77" s="133">
-        <f>D72</f>
-        <v>0</v>
-      </c>
-      <c r="C77" s="60"/>
-      <c r="D77" s="60"/>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="60"/>
-      <c r="B78" s="60"/>
-      <c r="C78" s="60"/>
-      <c r="D78" s="60"/>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="181" t="s">
-        <v>103</v>
-      </c>
-      <c r="B79" s="181"/>
-      <c r="C79" s="181"/>
-      <c r="D79" s="181"/>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="181"/>
-      <c r="B80" s="181"/>
-      <c r="C80" s="181"/>
-      <c r="D80" s="181"/>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="181"/>
-      <c r="B81" s="181"/>
-      <c r="C81" s="181"/>
-      <c r="D81" s="181"/>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="181"/>
-      <c r="B82" s="181"/>
-      <c r="C82" s="181"/>
-      <c r="D82" s="181"/>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="181"/>
-      <c r="B83" s="181"/>
-      <c r="C83" s="181"/>
-      <c r="D83" s="181"/>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="181"/>
-      <c r="B84" s="181"/>
-      <c r="C84" s="181"/>
-      <c r="D84" s="181"/>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="60"/>
-      <c r="B85" s="60"/>
-      <c r="C85" s="60"/>
-      <c r="D85" s="60"/>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="60"/>
-      <c r="B86" s="60"/>
-      <c r="C86" s="60"/>
-      <c r="D86" s="60"/>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="60"/>
-      <c r="B87" s="60"/>
-      <c r="C87" s="60"/>
-      <c r="D87" s="60"/>
-    </row>
-    <row r="88" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A88" s="135" t="s">
-        <v>44</v>
-      </c>
-      <c r="B88" s="136"/>
-      <c r="C88" s="60"/>
-      <c r="D88" s="60"/>
-    </row>
-    <row r="89" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A89" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B89" s="137">
-        <v>87629.73</v>
-      </c>
-      <c r="C89" s="60"/>
-    </row>
-    <row r="90" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A90" s="138" t="s">
-        <v>52</v>
-      </c>
-      <c r="B90" s="54">
-        <f>PRORRATEO!H18</f>
-        <v>890688.32</v>
-      </c>
-      <c r="C90" s="60"/>
-    </row>
-    <row r="91" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A91" s="138" t="s">
-        <v>51</v>
-      </c>
-      <c r="B91" s="54">
-        <f>B100</f>
-        <v>0</v>
-      </c>
-      <c r="C91" s="60"/>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="140" t="s">
+      <c r="B92" s="53">
+        <f>-B75</f>
+        <v>-1038315.79</v>
+      </c>
+      <c r="C92" s="59"/>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="138" t="s">
         <v>35</v>
       </c>
-      <c r="B92" s="54">
-        <f>-B75</f>
-        <v>-1029707.8300000001</v>
-      </c>
-      <c r="C92" s="60"/>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="139" t="s">
-        <v>36</v>
-      </c>
-      <c r="B93" s="54">
+      <c r="B93" s="53">
         <f>-(B76)</f>
         <v>0</v>
       </c>
-      <c r="C93" s="60"/>
+      <c r="C93" s="59"/>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B94" s="97">
+      <c r="B94" s="96">
         <f>SUM(B89:B93)</f>
-        <v>-51389.780000000144</v>
-      </c>
-      <c r="C94" s="124"/>
+        <v>-219783.18000000005</v>
+      </c>
+      <c r="C94" s="123"/>
     </row>
     <row r="95" spans="1:4" ht="34.5" customHeight="1">
-      <c r="B95" s="16"/>
-      <c r="C95" s="17"/>
-      <c r="D95" s="124"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="123"/>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="153" t="s">
-        <v>43</v>
-      </c>
-      <c r="B96" s="153"/>
+      <c r="A96" s="149" t="s">
+        <v>42</v>
+      </c>
+      <c r="B96" s="149"/>
     </row>
     <row r="97" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A97" s="153"/>
-      <c r="B97" s="153"/>
+      <c r="A97" s="149"/>
+      <c r="B97" s="149"/>
     </row>
     <row r="98" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A98" s="66"/>
-      <c r="B98" s="12"/>
+      <c r="A98" s="65"/>
+      <c r="B98" s="11"/>
     </row>
     <row r="99" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A99" s="66"/>
-      <c r="B99" s="12"/>
+      <c r="A99" s="65"/>
+      <c r="B99" s="11"/>
     </row>
     <row r="100" spans="1:12">
-      <c r="A100" s="18" t="s">
+      <c r="A100" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B100" s="67">
+      <c r="B100" s="66">
         <f>SUM(B98:B99)</f>
         <v>0</v>
       </c>
@@ -2948,173 +2942,173 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
-      <c r="A1" s="98"/>
-      <c r="B1" s="162" t="str">
+      <c r="A1" s="97"/>
+      <c r="B1" s="155" t="str">
         <f>RESUMEN!A4</f>
         <v>TRANSFERIR A  : Cuenta SANTANDER  533-033257/4 CBU :  0720533020000003325740 - CUIT: 30-71953248-5</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
-      <c r="K1" s="162"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="100"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="155"/>
+      <c r="K1" s="155"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="99"/>
     </row>
     <row r="2" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A2" s="101"/>
-      <c r="B2" s="163"/>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102" t="s">
+      <c r="A2" s="100"/>
+      <c r="B2" s="156"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101" t="s">
         <v>4</v>
       </c>
       <c r="N2" s="2"/>
-      <c r="O2" s="109">
-        <v>1000000</v>
-      </c>
-      <c r="P2" s="103"/>
+      <c r="O2" s="108">
+        <v>1400000</v>
+      </c>
+      <c r="P2" s="102"/>
       <c r="Q2" s="4"/>
       <c r="R2">
         <v>1406361.51</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="164"/>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="164"/>
-      <c r="K3" s="164"/>
-      <c r="L3" s="105"/>
-      <c r="M3" s="105" t="s">
-        <v>53</v>
-      </c>
-      <c r="N3" s="106"/>
-      <c r="O3" s="110">
-        <v>0</v>
-      </c>
-      <c r="P3" s="107"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="104"/>
+      <c r="M3" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" s="105"/>
+      <c r="O3" s="109">
+        <v>0</v>
+      </c>
+      <c r="P3" s="106"/>
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="174" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="175"/>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="175"/>
-      <c r="L4" s="175"/>
-      <c r="M4" s="175"/>
-      <c r="N4" s="175"/>
-      <c r="O4" s="175"/>
-      <c r="P4" s="176"/>
+      <c r="B4" s="168" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="169"/>
+      <c r="I4" s="169"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="169"/>
+      <c r="P4" s="170"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="160" t="s">
+      <c r="B5" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="161" t="s">
+      <c r="C5" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="161" t="s">
+      <c r="D5" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="161" t="s">
+      <c r="E5" s="160" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="160" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="160" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="160" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="160" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="161" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="161" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="161" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="161" t="s">
+      <c r="J5" s="164" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="170" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="168" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="168" t="s">
+      <c r="K5" s="162" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="162" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="168" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" s="172" t="s">
-        <v>48</v>
-      </c>
-      <c r="O5" s="86" t="s">
+      <c r="M5" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="166" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="165" t="s">
+      <c r="O5" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="S5" s="17"/>
-      <c r="T5" s="16"/>
+      <c r="P5" s="158" t="s">
+        <v>45</v>
+      </c>
+      <c r="S5" s="16"/>
+      <c r="T5" s="15"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="159"/>
-      <c r="B6" s="160"/>
-      <c r="C6" s="161"/>
-      <c r="D6" s="161"/>
-      <c r="E6" s="167"/>
-      <c r="F6" s="161"/>
-      <c r="G6" s="161"/>
-      <c r="H6" s="161"/>
-      <c r="I6" s="167"/>
-      <c r="J6" s="171"/>
-      <c r="K6" s="169"/>
-      <c r="L6" s="168"/>
-      <c r="M6" s="169"/>
-      <c r="N6" s="173"/>
-      <c r="O6" s="22" t="str">
+      <c r="A6" s="172"/>
+      <c r="B6" s="173"/>
+      <c r="C6" s="160"/>
+      <c r="D6" s="160"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="160"/>
+      <c r="I6" s="161"/>
+      <c r="J6" s="165"/>
+      <c r="K6" s="163"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="163"/>
+      <c r="N6" s="167"/>
+      <c r="O6" s="21" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="P6" s="165"/>
-      <c r="S6" s="16">
+      <c r="P6" s="158"/>
+      <c r="S6" s="15">
         <v>65160</v>
       </c>
-      <c r="T6" s="16">
+      <c r="T6" s="15">
         <v>157470</v>
       </c>
-      <c r="U6" s="17">
+      <c r="U6" s="16">
         <f>T6+S6</f>
         <v>222630</v>
       </c>
@@ -3123,63 +3117,63 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="77">
+      <c r="B7" s="76">
         <v>1</v>
       </c>
-      <c r="C7" s="77" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="77" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" s="77"/>
-      <c r="F7" s="90">
+      <c r="C7" s="76" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="76"/>
+      <c r="F7" s="89">
         <v>11.2</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="28">
         <v>1487190.01</v>
       </c>
-      <c r="H7" s="29">
-        <v>0</v>
-      </c>
-      <c r="I7" s="30"/>
-      <c r="J7" s="91">
+      <c r="H7" s="28">
+        <v>0</v>
+      </c>
+      <c r="I7" s="29"/>
+      <c r="J7" s="90">
         <f>G7-H7</f>
         <v>1487190.01</v>
       </c>
-      <c r="K7" s="91">
+      <c r="K7" s="90">
         <f>IF(J7&gt;0,J7*3%,0)</f>
         <v>44615.700299999997</v>
       </c>
-      <c r="L7" s="141">
+      <c r="L7" s="140">
         <f>O$3*F7%</f>
         <v>0</v>
       </c>
-      <c r="M7" s="92">
+      <c r="M7" s="91">
         <f>O$2*F7%</f>
-        <v>111999.99999999999</v>
-      </c>
-      <c r="N7" s="93">
-        <v>0</v>
-      </c>
-      <c r="O7" s="94">
+        <v>156799.99999999997</v>
+      </c>
+      <c r="N7" s="92">
+        <v>0</v>
+      </c>
+      <c r="O7" s="93">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>1643806.01</v>
-      </c>
-      <c r="P7" s="95">
+        <v>1688606.01</v>
+      </c>
+      <c r="P7" s="94">
         <f t="shared" ref="P7:P16" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>1693120.01</v>
-      </c>
-      <c r="Q7" s="17">
+        <v>1739264.01</v>
+      </c>
+      <c r="Q7" s="16">
         <v>0.01</v>
       </c>
-      <c r="S7" s="16">
+      <c r="S7" s="15">
         <v>66960</v>
       </c>
-      <c r="T7" s="16">
+      <c r="T7" s="15">
         <v>161820</v>
       </c>
-      <c r="U7" s="17">
+      <c r="U7" s="16">
         <f t="shared" ref="U7:U16" si="1">T7+S7</f>
         <v>228780</v>
       </c>
@@ -3188,65 +3182,65 @@
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="23">
         <v>2</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="27">
+      <c r="C8" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="26">
         <v>11.2</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="27">
         <v>413951.02</v>
       </c>
-      <c r="H8" s="29">
-        <v>0</v>
-      </c>
-      <c r="I8" s="30"/>
-      <c r="J8" s="31">
+      <c r="H8" s="28">
+        <v>0</v>
+      </c>
+      <c r="I8" s="29"/>
+      <c r="J8" s="30">
         <f t="shared" ref="J8:J16" si="2">G8-H8</f>
         <v>413951.02</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="30">
         <f t="shared" ref="K8:K16" si="3">IF(J8&gt;0,J8*3%,0)</f>
         <v>12418.5306</v>
       </c>
-      <c r="L8" s="32">
+      <c r="L8" s="31">
         <f t="shared" ref="L8:L17" si="4">O$3*F8%</f>
         <v>0</v>
       </c>
-      <c r="M8" s="32">
+      <c r="M8" s="31">
         <f t="shared" ref="M8:M17" si="5">O$2*F8%</f>
-        <v>111999.99999999999</v>
-      </c>
-      <c r="N8" s="33">
-        <v>0</v>
-      </c>
-      <c r="O8" s="34">
+        <v>156799.99999999997</v>
+      </c>
+      <c r="N8" s="32">
+        <v>0</v>
+      </c>
+      <c r="O8" s="33">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>538370.02</v>
-      </c>
-      <c r="P8" s="35">
+        <v>583170.02</v>
+      </c>
+      <c r="P8" s="34">
         <f t="shared" si="0"/>
-        <v>554521.02</v>
-      </c>
-      <c r="Q8" s="17">
+        <v>600665.02</v>
+      </c>
+      <c r="Q8" s="16">
         <f>Q7+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="R8" s="17"/>
-      <c r="S8" s="16">
+      <c r="R8" s="16"/>
+      <c r="S8" s="15">
         <v>41700</v>
       </c>
-      <c r="T8" s="16">
+      <c r="T8" s="15">
         <v>100775</v>
       </c>
-      <c r="U8" s="17">
+      <c r="U8" s="16">
         <f t="shared" si="1"/>
         <v>142475</v>
       </c>
@@ -3255,64 +3249,64 @@
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <v>3</v>
       </c>
-      <c r="C9" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="88" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="90">
+      <c r="C9" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="87" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="76"/>
+      <c r="F9" s="89">
         <v>8.9</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>180670.03</v>
       </c>
-      <c r="H9" s="180">
+      <c r="H9" s="28">
         <v>187000</v>
       </c>
-      <c r="I9" s="30"/>
-      <c r="J9" s="91">
+      <c r="I9" s="29"/>
+      <c r="J9" s="90">
         <f t="shared" si="2"/>
         <v>-6329.9700000000012</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="91">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M9" s="92">
+      <c r="M9" s="91">
         <f t="shared" si="5"/>
-        <v>89000.000000000015</v>
-      </c>
-      <c r="N9" s="93">
-        <v>0</v>
-      </c>
-      <c r="O9" s="94">
+        <v>124600.00000000001</v>
+      </c>
+      <c r="N9" s="92">
+        <v>0</v>
+      </c>
+      <c r="O9" s="93">
         <f t="shared" ref="O9:O16" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>82670.03</v>
-      </c>
-      <c r="P9" s="95">
+        <v>118270.03</v>
+      </c>
+      <c r="P9" s="94">
         <f t="shared" si="0"/>
-        <v>85150.03</v>
-      </c>
-      <c r="Q9" s="17">
+        <v>121818.03</v>
+      </c>
+      <c r="Q9" s="16">
         <f t="shared" ref="Q9:Q16" si="7">Q8+0.01</f>
         <v>0.03</v>
       </c>
-      <c r="S9" s="16">
+      <c r="S9" s="15">
         <v>44220</v>
       </c>
-      <c r="T9" s="16">
+      <c r="T9" s="15">
         <v>106865</v>
       </c>
-      <c r="U9" s="17">
+      <c r="U9" s="16">
         <f t="shared" si="1"/>
         <v>151085</v>
       </c>
@@ -3321,64 +3315,64 @@
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="23">
         <v>4</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="24"/>
-      <c r="F10" s="90">
+      <c r="C10" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" s="23"/>
+      <c r="F10" s="89">
         <v>8.9</v>
       </c>
-      <c r="G10" s="28">
-        <v>91722.04</v>
-      </c>
-      <c r="H10" s="29">
-        <v>0</v>
-      </c>
-      <c r="I10" s="30"/>
-      <c r="J10" s="31">
+      <c r="G10" s="27">
+        <v>94474.04</v>
+      </c>
+      <c r="H10" s="28">
+        <v>95000</v>
+      </c>
+      <c r="I10" s="29"/>
+      <c r="J10" s="30">
         <f t="shared" si="2"/>
-        <v>91722.04</v>
-      </c>
-      <c r="K10" s="31">
+        <v>-525.9600000000064</v>
+      </c>
+      <c r="K10" s="30">
         <f t="shared" si="3"/>
-        <v>2751.6611999999996</v>
-      </c>
-      <c r="L10" s="32">
+        <v>0</v>
+      </c>
+      <c r="L10" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M10" s="32">
+      <c r="M10" s="31">
         <f t="shared" si="5"/>
-        <v>89000.000000000015</v>
-      </c>
-      <c r="N10" s="33">
-        <v>0</v>
-      </c>
-      <c r="O10" s="34">
+        <v>124600.00000000001</v>
+      </c>
+      <c r="N10" s="32">
+        <v>0</v>
+      </c>
+      <c r="O10" s="33">
         <f t="shared" si="6"/>
-        <v>183474.04</v>
-      </c>
-      <c r="P10" s="35">
+        <v>124074.04</v>
+      </c>
+      <c r="P10" s="34">
         <f t="shared" si="0"/>
-        <v>188978.04</v>
-      </c>
-      <c r="Q10" s="17">
+        <v>127796.04</v>
+      </c>
+      <c r="Q10" s="16">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
-      <c r="S10" s="16">
+      <c r="S10" s="15">
         <v>64080</v>
       </c>
-      <c r="T10" s="16">
+      <c r="T10" s="15">
         <v>154860</v>
       </c>
-      <c r="U10" s="17">
+      <c r="U10" s="16">
         <f t="shared" si="1"/>
         <v>218940</v>
       </c>
@@ -3387,64 +3381,64 @@
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="23">
         <v>5</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="27">
+      <c r="C11" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="26">
         <v>9.8000000000000007</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="27">
         <v>98000.05</v>
       </c>
-      <c r="H11" s="180">
+      <c r="H11" s="28">
         <v>98100</v>
       </c>
-      <c r="I11" s="30"/>
-      <c r="J11" s="31">
+      <c r="I11" s="29"/>
+      <c r="J11" s="30">
         <f t="shared" si="2"/>
         <v>-99.94999999999709</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L11" s="32">
+      <c r="L11" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M11" s="32">
+      <c r="M11" s="31">
         <f t="shared" si="5"/>
-        <v>98000</v>
-      </c>
-      <c r="N11" s="33">
-        <v>0</v>
-      </c>
-      <c r="O11" s="34">
+        <v>137200</v>
+      </c>
+      <c r="N11" s="32">
+        <v>0</v>
+      </c>
+      <c r="O11" s="33">
         <f t="shared" si="6"/>
-        <v>97900.05</v>
-      </c>
-      <c r="P11" s="35">
+        <v>137100.04999999999</v>
+      </c>
+      <c r="P11" s="34">
         <f t="shared" si="0"/>
-        <v>100837.05</v>
-      </c>
-      <c r="Q11" s="17">
+        <v>141213.04999999999</v>
+      </c>
+      <c r="Q11" s="16">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
-      <c r="S11" s="16">
+      <c r="S11" s="15">
         <v>41700</v>
       </c>
-      <c r="T11" s="16">
+      <c r="T11" s="15">
         <v>100775</v>
       </c>
-      <c r="U11" s="17">
+      <c r="U11" s="16">
         <f t="shared" si="1"/>
         <v>142475</v>
       </c>
@@ -3453,65 +3447,65 @@
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="23">
         <v>6</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="24"/>
-      <c r="F12" s="27">
+      <c r="C12" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="23"/>
+      <c r="F12" s="26">
         <v>9.8000000000000007</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="27">
         <v>98000.06</v>
       </c>
-      <c r="H12" s="180">
+      <c r="H12" s="28">
         <f>G12</f>
         <v>98000.06</v>
       </c>
-      <c r="I12" s="30"/>
-      <c r="J12" s="31">
+      <c r="I12" s="29"/>
+      <c r="J12" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K12" s="31">
+      <c r="K12" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L12" s="32">
+      <c r="L12" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="32">
+      <c r="M12" s="31">
         <f t="shared" si="5"/>
-        <v>98000</v>
-      </c>
-      <c r="N12" s="123">
-        <v>0</v>
-      </c>
-      <c r="O12" s="34">
+        <v>137200</v>
+      </c>
+      <c r="N12" s="122">
+        <v>0</v>
+      </c>
+      <c r="O12" s="33">
         <f>ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>98000.06</v>
-      </c>
-      <c r="P12" s="35">
+        <v>137200.06</v>
+      </c>
+      <c r="P12" s="34">
         <f t="shared" si="0"/>
-        <v>100940.06</v>
-      </c>
-      <c r="Q12" s="17">
+        <v>141316.06</v>
+      </c>
+      <c r="Q12" s="16">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="S12" s="16">
+      <c r="S12" s="15">
         <v>41340</v>
       </c>
-      <c r="T12" s="16">
+      <c r="T12" s="15">
         <v>99905</v>
       </c>
-      <c r="U12" s="17">
+      <c r="U12" s="16">
         <f t="shared" si="1"/>
         <v>141245</v>
       </c>
@@ -3520,65 +3514,65 @@
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="23">
         <v>7</v>
       </c>
-      <c r="C13" s="77" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="24"/>
-      <c r="F13" s="90">
+      <c r="C13" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="23"/>
+      <c r="F13" s="89">
         <v>8.9</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="27">
         <v>89000.07</v>
       </c>
-      <c r="H13" s="180">
+      <c r="H13" s="28">
         <v>91670.07</v>
       </c>
-      <c r="I13" s="30"/>
-      <c r="J13" s="31">
+      <c r="I13" s="29"/>
+      <c r="J13" s="30">
         <f t="shared" si="2"/>
         <v>-2670</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L13" s="32">
+      <c r="L13" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M13" s="32">
+      <c r="M13" s="31">
         <f t="shared" si="5"/>
-        <v>89000.000000000015</v>
-      </c>
-      <c r="N13" s="33">
-        <v>0</v>
-      </c>
-      <c r="O13" s="34">
+        <v>124600.00000000001</v>
+      </c>
+      <c r="N13" s="32">
+        <v>0</v>
+      </c>
+      <c r="O13" s="33">
         <f t="shared" si="6"/>
-        <v>86330.07</v>
-      </c>
-      <c r="P13" s="35">
+        <v>121930.07</v>
+      </c>
+      <c r="P13" s="34">
         <f t="shared" si="0"/>
-        <v>88920.07</v>
-      </c>
-      <c r="Q13" s="17">
+        <v>125588.07</v>
+      </c>
+      <c r="Q13" s="16">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="R13" s="75"/>
-      <c r="S13" s="108">
+      <c r="R13" s="74"/>
+      <c r="S13" s="107">
         <v>64080</v>
       </c>
-      <c r="T13" s="16">
+      <c r="T13" s="15">
         <v>154860</v>
       </c>
-      <c r="U13" s="17">
+      <c r="U13" s="16">
         <f t="shared" si="1"/>
         <v>218940</v>
       </c>
@@ -3587,66 +3581,66 @@
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="23">
         <v>8</v>
       </c>
-      <c r="C14" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="90">
+      <c r="C14" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="89">
         <v>8.9</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="27">
         <v>185198.07999999999</v>
       </c>
-      <c r="H14" s="180">
+      <c r="H14" s="28">
         <v>185198</v>
       </c>
-      <c r="I14" s="30"/>
-      <c r="J14" s="31">
+      <c r="I14" s="29"/>
+      <c r="J14" s="30">
         <f t="shared" si="2"/>
         <v>7.9999999987194315E-2</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="30">
         <f t="shared" si="3"/>
         <v>2.3999999996158292E-3</v>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="31">
         <f t="shared" si="5"/>
-        <v>89000.000000000015</v>
-      </c>
-      <c r="N14" s="33">
-        <v>0</v>
-      </c>
-      <c r="O14" s="34">
+        <v>124600.00000000001</v>
+      </c>
+      <c r="N14" s="32">
+        <v>0</v>
+      </c>
+      <c r="O14" s="33">
         <f t="shared" si="6"/>
-        <v>89000.08</v>
-      </c>
-      <c r="P14" s="35">
+        <v>124600.08</v>
+      </c>
+      <c r="P14" s="34">
         <f t="shared" si="0"/>
-        <v>91670.080000000002</v>
-      </c>
-      <c r="Q14" s="17">
+        <v>128338.08</v>
+      </c>
+      <c r="Q14" s="16">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
-      <c r="S14" s="16">
+      <c r="S14" s="15">
         <v>41700</v>
       </c>
-      <c r="T14" s="16">
+      <c r="T14" s="15">
         <v>100775</v>
       </c>
-      <c r="U14" s="17">
+      <c r="U14" s="16">
         <f t="shared" si="1"/>
         <v>142475</v>
       </c>
@@ -3655,65 +3649,65 @@
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="77">
+      <c r="B15" s="76">
         <v>9</v>
       </c>
-      <c r="C15" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="77" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="89" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" s="27">
+      <c r="C15" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="88" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="26">
         <v>11.2</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="28">
         <v>112000.09</v>
       </c>
-      <c r="H15" s="180">
+      <c r="H15" s="28">
         <v>115360.09</v>
       </c>
-      <c r="I15" s="30"/>
-      <c r="J15" s="91">
+      <c r="I15" s="29"/>
+      <c r="J15" s="90">
         <f t="shared" si="2"/>
         <v>-3360</v>
       </c>
-      <c r="K15" s="91">
-        <v>0</v>
-      </c>
-      <c r="L15" s="92">
+      <c r="K15" s="90">
+        <v>0</v>
+      </c>
+      <c r="L15" s="91">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M15" s="92">
+      <c r="M15" s="91">
         <f t="shared" si="5"/>
-        <v>111999.99999999999</v>
-      </c>
-      <c r="N15" s="93">
-        <v>0</v>
-      </c>
-      <c r="O15" s="94">
+        <v>156799.99999999997</v>
+      </c>
+      <c r="N15" s="92">
+        <v>0</v>
+      </c>
+      <c r="O15" s="93">
         <f t="shared" si="6"/>
-        <v>108640.09</v>
-      </c>
-      <c r="P15" s="95">
+        <v>153440.09</v>
+      </c>
+      <c r="P15" s="94">
         <f t="shared" si="0"/>
-        <v>111899.09</v>
-      </c>
-      <c r="Q15" s="17">
+        <v>158043.09</v>
+      </c>
+      <c r="Q15" s="16">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
-      <c r="S15" s="16">
+      <c r="S15" s="15">
         <v>41340</v>
       </c>
-      <c r="T15" s="16">
+      <c r="T15" s="15">
         <v>99905</v>
       </c>
-      <c r="U15" s="17">
+      <c r="U15" s="16">
         <f t="shared" si="1"/>
         <v>141245</v>
       </c>
@@ -3722,64 +3716,64 @@
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="77">
+      <c r="B16" s="76">
         <v>10</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" s="89"/>
-      <c r="F16" s="27">
+      <c r="C16" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="88"/>
+      <c r="F16" s="26">
         <v>11.2</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="27">
         <v>112000.1</v>
       </c>
-      <c r="H16" s="180">
+      <c r="H16" s="28">
         <v>115360.1</v>
       </c>
-      <c r="I16" s="30"/>
-      <c r="J16" s="31">
+      <c r="I16" s="29"/>
+      <c r="J16" s="30">
         <f t="shared" si="2"/>
         <v>-3360</v>
       </c>
-      <c r="K16" s="31">
+      <c r="K16" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L16" s="32">
+      <c r="L16" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M16" s="32">
+      <c r="M16" s="31">
         <f t="shared" si="5"/>
-        <v>111999.99999999999</v>
-      </c>
-      <c r="N16" s="33">
-        <v>0</v>
-      </c>
-      <c r="O16" s="34">
+        <v>156799.99999999997</v>
+      </c>
+      <c r="N16" s="32">
+        <v>0</v>
+      </c>
+      <c r="O16" s="33">
         <f t="shared" si="6"/>
-        <v>108640.1</v>
-      </c>
-      <c r="P16" s="35">
+        <v>153440.1</v>
+      </c>
+      <c r="P16" s="34">
         <f t="shared" si="0"/>
-        <v>111899.1</v>
-      </c>
-      <c r="Q16" s="17">
+        <v>158043.1</v>
+      </c>
+      <c r="Q16" s="16">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
-      <c r="S16" s="16">
+      <c r="S16" s="15">
         <v>71280</v>
       </c>
-      <c r="T16" s="16">
+      <c r="T16" s="15">
         <v>172260</v>
       </c>
-      <c r="U16" s="17">
+      <c r="U16" s="16">
         <f t="shared" si="1"/>
         <v>243540</v>
       </c>
@@ -3788,172 +3782,177 @@
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" s="29"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="38" t="e">
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="28"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="37" t="e">
         <f t="shared" ref="J17" si="8">G17-H17</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K17" s="31"/>
-      <c r="L17" s="32">
+      <c r="K17" s="30"/>
+      <c r="L17" s="31">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M17" s="39">
+      <c r="M17" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N17" s="40">
-        <v>0</v>
-      </c>
-      <c r="O17" s="34"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="17"/>
+      <c r="N17" s="39">
+        <v>0</v>
+      </c>
+      <c r="O17" s="33"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="16"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" thickBot="1">
-      <c r="B18" s="41"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="44">
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="43">
         <f>SUM(F7:F17)</f>
         <v>100.00000000000001</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="19">
         <f>SUM(G7:G17)</f>
-        <v>2867731.55</v>
-      </c>
-      <c r="H18" s="20">
+        <v>2870483.55</v>
+      </c>
+      <c r="H18" s="19">
         <f>SUM(H7:H17)</f>
-        <v>890688.32</v>
-      </c>
-      <c r="I18" s="23">
+        <v>985688.32</v>
+      </c>
+      <c r="I18" s="22">
         <f>SUM(I7:I17)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23">
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22">
         <f>SUM(L7:L17)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="22">
         <f>SUM(M7:M17)</f>
-        <v>1000000</v>
-      </c>
-      <c r="N18" s="23">
+        <v>1400000</v>
+      </c>
+      <c r="N18" s="22">
         <f>SUM(N7:N17)</f>
         <v>0</v>
       </c>
-      <c r="O18" s="45">
+      <c r="O18" s="44">
         <f>SUM(O7:O16)</f>
-        <v>3036830.55</v>
-      </c>
-      <c r="P18" s="45">
+        <v>3341830.55</v>
+      </c>
+      <c r="P18" s="44">
         <f>SUM(P7:P16)</f>
-        <v>3127934.55</v>
+        <v>3442084.55</v>
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="D21" s="166" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="166"/>
-      <c r="F21" s="166"/>
-      <c r="G21" s="166"/>
-      <c r="H21" s="166"/>
-      <c r="I21" s="166"/>
-      <c r="J21" s="166"/>
-      <c r="K21" s="166"/>
-      <c r="L21" s="166"/>
-      <c r="M21" s="166"/>
-      <c r="N21" s="166"/>
-      <c r="O21" s="166"/>
+      <c r="D21" s="159" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="159"/>
+      <c r="F21" s="159"/>
+      <c r="G21" s="159"/>
+      <c r="H21" s="159"/>
+      <c r="I21" s="159"/>
+      <c r="J21" s="159"/>
+      <c r="K21" s="159"/>
+      <c r="L21" s="159"/>
+      <c r="M21" s="159"/>
+      <c r="N21" s="159"/>
+      <c r="O21" s="159"/>
     </row>
     <row r="22" spans="1:17">
-      <c r="D22" s="166"/>
-      <c r="E22" s="166"/>
-      <c r="F22" s="166"/>
-      <c r="G22" s="166"/>
-      <c r="H22" s="166"/>
-      <c r="I22" s="166"/>
-      <c r="J22" s="166"/>
-      <c r="K22" s="166"/>
-      <c r="L22" s="166"/>
-      <c r="M22" s="166"/>
-      <c r="N22" s="166"/>
-      <c r="O22" s="166"/>
+      <c r="D22" s="159"/>
+      <c r="E22" s="159"/>
+      <c r="F22" s="159"/>
+      <c r="G22" s="159"/>
+      <c r="H22" s="159"/>
+      <c r="I22" s="159"/>
+      <c r="J22" s="159"/>
+      <c r="K22" s="159"/>
+      <c r="L22" s="159"/>
+      <c r="M22" s="159"/>
+      <c r="N22" s="159"/>
+      <c r="O22" s="159"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="D23" s="166"/>
-      <c r="E23" s="166"/>
-      <c r="F23" s="166"/>
-      <c r="G23" s="166"/>
-      <c r="H23" s="166"/>
-      <c r="I23" s="166"/>
-      <c r="J23" s="166"/>
-      <c r="K23" s="166"/>
-      <c r="L23" s="166"/>
-      <c r="M23" s="166"/>
-      <c r="N23" s="166"/>
-      <c r="O23" s="166"/>
+      <c r="D23" s="159"/>
+      <c r="E23" s="159"/>
+      <c r="F23" s="159"/>
+      <c r="G23" s="159"/>
+      <c r="H23" s="159"/>
+      <c r="I23" s="159"/>
+      <c r="J23" s="159"/>
+      <c r="K23" s="159"/>
+      <c r="L23" s="159"/>
+      <c r="M23" s="159"/>
+      <c r="N23" s="159"/>
+      <c r="O23" s="159"/>
     </row>
     <row r="24" spans="1:17">
-      <c r="D24" s="166"/>
-      <c r="E24" s="166"/>
-      <c r="F24" s="166"/>
-      <c r="G24" s="166"/>
-      <c r="H24" s="166"/>
-      <c r="I24" s="166"/>
-      <c r="J24" s="166"/>
-      <c r="K24" s="166"/>
-      <c r="L24" s="166"/>
-      <c r="M24" s="166"/>
-      <c r="N24" s="166"/>
-      <c r="O24" s="166"/>
+      <c r="D24" s="159"/>
+      <c r="E24" s="159"/>
+      <c r="F24" s="159"/>
+      <c r="G24" s="159"/>
+      <c r="H24" s="159"/>
+      <c r="I24" s="159"/>
+      <c r="J24" s="159"/>
+      <c r="K24" s="159"/>
+      <c r="L24" s="159"/>
+      <c r="M24" s="159"/>
+      <c r="N24" s="159"/>
+      <c r="O24" s="159"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="D25" s="166"/>
-      <c r="E25" s="166"/>
-      <c r="F25" s="166"/>
-      <c r="G25" s="166"/>
-      <c r="H25" s="166"/>
-      <c r="I25" s="166"/>
-      <c r="J25" s="166"/>
-      <c r="K25" s="166"/>
-      <c r="L25" s="166"/>
-      <c r="M25" s="166"/>
-      <c r="N25" s="166"/>
-      <c r="O25" s="166"/>
+      <c r="D25" s="159"/>
+      <c r="E25" s="159"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="159"/>
+      <c r="I25" s="159"/>
+      <c r="J25" s="159"/>
+      <c r="K25" s="159"/>
+      <c r="L25" s="159"/>
+      <c r="M25" s="159"/>
+      <c r="N25" s="159"/>
+      <c r="O25" s="159"/>
     </row>
     <row r="26" spans="1:17" ht="65.25" customHeight="1">
-      <c r="D26" s="166"/>
-      <c r="E26" s="166"/>
-      <c r="F26" s="166"/>
-      <c r="G26" s="166"/>
-      <c r="H26" s="166"/>
-      <c r="I26" s="166"/>
-      <c r="J26" s="166"/>
-      <c r="K26" s="166"/>
-      <c r="L26" s="166"/>
-      <c r="M26" s="166"/>
-      <c r="N26" s="166"/>
-      <c r="O26" s="166"/>
+      <c r="D26" s="159"/>
+      <c r="E26" s="159"/>
+      <c r="F26" s="159"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="159"/>
+      <c r="I26" s="159"/>
+      <c r="J26" s="159"/>
+      <c r="K26" s="159"/>
+      <c r="L26" s="159"/>
+      <c r="M26" s="159"/>
+      <c r="N26" s="159"/>
+      <c r="O26" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D21:O26"/>
@@ -3967,11 +3966,6 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>

--- a/2026/GENERAL PAZ 138/Agosto/Agosto GRAL PAZ 138.xlsx
+++ b/2026/GENERAL PAZ 138/Agosto/Agosto GRAL PAZ 138.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31280EF-45F5-4834-957B-063CE6A7EADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCFEAC7-20A2-4846-A773-71000D8A0CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1551,93 +1551,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="8" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1645,6 +1558,93 @@
     <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -2111,68 +2111,68 @@
       <c r="D3" s="69"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="145" t="s">
+      <c r="A4" s="151" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="145"/>
+      <c r="B4" s="151"/>
       <c r="C4" s="70"/>
       <c r="D4" s="70"/>
     </row>
     <row r="5" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A5" s="145"/>
-      <c r="B5" s="145"/>
+      <c r="A5" s="151"/>
+      <c r="B5" s="151"/>
       <c r="C5" s="70"/>
       <c r="D5" s="70"/>
     </row>
     <row r="6" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A6" s="145"/>
-      <c r="B6" s="145"/>
+      <c r="A6" s="151"/>
+      <c r="B6" s="151"/>
       <c r="C6" s="70"/>
       <c r="D6" s="70"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="145"/>
-      <c r="B7" s="145"/>
+      <c r="A7" s="151"/>
+      <c r="B7" s="151"/>
       <c r="C7" s="70"/>
       <c r="D7" s="70"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="159" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="153"/>
+      <c r="B10" s="159"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="153"/>
+      <c r="B11" s="159"/>
     </row>
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="148"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="148"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="148"/>
-      <c r="B15" s="148"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="148"/>
+      <c r="A15" s="154"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="148"/>
-      <c r="B16" s="148"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="148"/>
+      <c r="A16" s="154"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="148"/>
-      <c r="B17" s="148"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="148"/>
+      <c r="A17" s="154"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
+      <c r="D17" s="154"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
       <c r="A18" s="59"/>
@@ -2292,7 +2292,7 @@
       <c r="B32" s="144" t="s">
         <v>98</v>
       </c>
-      <c r="C32" s="174">
+      <c r="C32" s="145">
         <v>130000</v>
       </c>
       <c r="D32" s="80" t="s">
@@ -2306,7 +2306,7 @@
         <v>94</v>
       </c>
       <c r="B33" s="113"/>
-      <c r="C33" s="175">
+      <c r="C33" s="146">
         <v>70000</v>
       </c>
       <c r="D33" s="80" t="s">
@@ -2320,7 +2320,7 @@
         <v>95</v>
       </c>
       <c r="B34" s="113"/>
-      <c r="C34" s="175">
+      <c r="C34" s="146">
         <v>130000</v>
       </c>
       <c r="D34" s="80" t="s">
@@ -2349,11 +2349,11 @@
       <c r="D36" s="25"/>
     </row>
     <row r="37" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A37" s="146" t="s">
+      <c r="A37" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="147"/>
-      <c r="C37" s="176">
+      <c r="B37" s="153"/>
+      <c r="C37" s="147">
         <v>87914</v>
       </c>
       <c r="D37" s="79" t="s">
@@ -2361,11 +2361,11 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A38" s="146" t="s">
+      <c r="A38" s="152" t="s">
         <v>89</v>
       </c>
-      <c r="B38" s="147"/>
-      <c r="C38" s="177">
+      <c r="B38" s="153"/>
+      <c r="C38" s="148">
         <v>84333</v>
       </c>
       <c r="D38" s="143" t="s">
@@ -2480,7 +2480,7 @@
         <v>79</v>
       </c>
       <c r="B49" s="45"/>
-      <c r="C49" s="178">
+      <c r="C49" s="149">
         <v>204474.88</v>
       </c>
       <c r="D49" s="77" t="s">
@@ -2507,11 +2507,11 @@
       <c r="D51" s="52"/>
     </row>
     <row r="52" spans="1:6" ht="39.6" customHeight="1">
-      <c r="A52" s="146" t="s">
+      <c r="A52" s="152" t="s">
         <v>96</v>
       </c>
-      <c r="B52" s="147"/>
-      <c r="C52" s="178">
+      <c r="B52" s="153"/>
+      <c r="C52" s="149">
         <v>102680</v>
       </c>
       <c r="D52" s="75"/>
@@ -2563,11 +2563,11 @@
       <c r="D57" s="57"/>
     </row>
     <row r="58" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A58" s="150" t="s">
+      <c r="A58" s="156" t="s">
         <v>74</v>
       </c>
-      <c r="B58" s="151"/>
-      <c r="C58" s="152"/>
+      <c r="B58" s="157"/>
+      <c r="C58" s="158"/>
       <c r="D58" s="58">
         <f>1400000-1038315.79</f>
         <v>361684.20999999996</v>
@@ -2615,14 +2615,14 @@
       <c r="D63" s="64"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="146"/>
-      <c r="B64" s="147"/>
+      <c r="A64" s="152"/>
+      <c r="B64" s="153"/>
       <c r="C64" s="84"/>
       <c r="D64" s="75"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="146"/>
-      <c r="B65" s="147"/>
+      <c r="A65" s="152"/>
+      <c r="B65" s="153"/>
       <c r="C65" s="84"/>
       <c r="D65" s="51"/>
     </row>
@@ -2737,42 +2737,42 @@
       <c r="D78" s="59"/>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="154" t="s">
+      <c r="A79" s="160" t="s">
         <v>102</v>
       </c>
-      <c r="B79" s="154"/>
-      <c r="C79" s="154"/>
-      <c r="D79" s="154"/>
+      <c r="B79" s="160"/>
+      <c r="C79" s="160"/>
+      <c r="D79" s="160"/>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="154"/>
-      <c r="B80" s="154"/>
-      <c r="C80" s="154"/>
-      <c r="D80" s="154"/>
+      <c r="A80" s="160"/>
+      <c r="B80" s="160"/>
+      <c r="C80" s="160"/>
+      <c r="D80" s="160"/>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="154"/>
-      <c r="B81" s="154"/>
-      <c r="C81" s="154"/>
-      <c r="D81" s="154"/>
+      <c r="A81" s="160"/>
+      <c r="B81" s="160"/>
+      <c r="C81" s="160"/>
+      <c r="D81" s="160"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="154"/>
-      <c r="B82" s="154"/>
-      <c r="C82" s="154"/>
-      <c r="D82" s="154"/>
+      <c r="A82" s="160"/>
+      <c r="B82" s="160"/>
+      <c r="C82" s="160"/>
+      <c r="D82" s="160"/>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="154"/>
-      <c r="B83" s="154"/>
-      <c r="C83" s="154"/>
-      <c r="D83" s="154"/>
+      <c r="A83" s="160"/>
+      <c r="B83" s="160"/>
+      <c r="C83" s="160"/>
+      <c r="D83" s="160"/>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="154"/>
-      <c r="B84" s="154"/>
-      <c r="C84" s="154"/>
-      <c r="D84" s="154"/>
+      <c r="A84" s="160"/>
+      <c r="B84" s="160"/>
+      <c r="C84" s="160"/>
+      <c r="D84" s="160"/>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="59"/>
@@ -2801,7 +2801,7 @@
       <c r="D88" s="59"/>
     </row>
     <row r="89" spans="1:4" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A89" s="179" t="s">
+      <c r="A89" s="150" t="s">
         <v>105</v>
       </c>
       <c r="B89" s="136">
@@ -2865,14 +2865,14 @@
       <c r="D95" s="123"/>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="149" t="s">
+      <c r="A96" s="155" t="s">
         <v>42</v>
       </c>
-      <c r="B96" s="149"/>
+      <c r="B96" s="155"/>
     </row>
     <row r="97" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A97" s="149"/>
-      <c r="B97" s="149"/>
+      <c r="A97" s="155"/>
+      <c r="B97" s="155"/>
     </row>
     <row r="98" spans="1:12" ht="32.25" customHeight="1">
       <c r="A98" s="65"/>
@@ -2943,19 +2943,19 @@
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="97"/>
-      <c r="B1" s="155" t="str">
+      <c r="B1" s="165" t="str">
         <f>RESUMEN!A4</f>
         <v>TRANSFERIR A  : Cuenta SANTANDER  533-033257/4 CBU :  0720533020000003325740 - CUIT: 30-71953248-5</v>
       </c>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="98"/>
       <c r="M1" s="98"/>
       <c r="N1" s="98"/>
@@ -2964,16 +2964,16 @@
     </row>
     <row r="2" spans="1:21" ht="14.25" customHeight="1">
       <c r="A2" s="100"/>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
       <c r="L2" s="101"/>
       <c r="M2" s="101" t="s">
         <v>4</v>
@@ -2990,16 +2990,16 @@
     </row>
     <row r="3" spans="1:21" ht="16.5" customHeight="1" thickBot="1">
       <c r="A3" s="103"/>
-      <c r="B3" s="157"/>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="157"/>
-      <c r="J3" s="157"/>
-      <c r="K3" s="157"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="167"/>
+      <c r="I3" s="167"/>
+      <c r="J3" s="167"/>
+      <c r="K3" s="167"/>
       <c r="L3" s="104"/>
       <c r="M3" s="104" t="s">
         <v>52</v>
@@ -3012,96 +3012,96 @@
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="168" t="s">
+      <c r="B4" s="177" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="169"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="169"/>
-      <c r="I4" s="169"/>
-      <c r="J4" s="169"/>
-      <c r="K4" s="169"/>
-      <c r="L4" s="169"/>
-      <c r="M4" s="169"/>
-      <c r="N4" s="169"/>
-      <c r="O4" s="169"/>
-      <c r="P4" s="170"/>
+      <c r="C4" s="178"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="178"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="178"/>
+      <c r="K4" s="178"/>
+      <c r="L4" s="178"/>
+      <c r="M4" s="178"/>
+      <c r="N4" s="178"/>
+      <c r="O4" s="178"/>
+      <c r="P4" s="179"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="171" t="s">
+      <c r="A5" s="161" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="173" t="s">
+      <c r="B5" s="163" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="160" t="s">
+      <c r="C5" s="164" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="160" t="s">
+      <c r="D5" s="164" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="160" t="s">
+      <c r="E5" s="164" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="160" t="s">
+      <c r="F5" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="160" t="s">
+      <c r="G5" s="164" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="160" t="s">
+      <c r="H5" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="160" t="s">
+      <c r="I5" s="164" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="164" t="s">
+      <c r="J5" s="173" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="162" t="s">
+      <c r="K5" s="171" t="s">
         <v>37</v>
       </c>
-      <c r="L5" s="162" t="s">
+      <c r="L5" s="171" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="162" t="s">
+      <c r="M5" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="166" t="s">
+      <c r="N5" s="175" t="s">
         <v>47</v>
       </c>
       <c r="O5" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="158" t="s">
+      <c r="P5" s="168" t="s">
         <v>45</v>
       </c>
       <c r="S5" s="16"/>
       <c r="T5" s="15"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="172"/>
-      <c r="B6" s="173"/>
-      <c r="C6" s="160"/>
-      <c r="D6" s="160"/>
-      <c r="E6" s="161"/>
-      <c r="F6" s="160"/>
-      <c r="G6" s="160"/>
-      <c r="H6" s="160"/>
-      <c r="I6" s="161"/>
-      <c r="J6" s="165"/>
-      <c r="K6" s="163"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="163"/>
-      <c r="N6" s="167"/>
+      <c r="A6" s="162"/>
+      <c r="B6" s="163"/>
+      <c r="C6" s="164"/>
+      <c r="D6" s="164"/>
+      <c r="E6" s="170"/>
+      <c r="F6" s="164"/>
+      <c r="G6" s="164"/>
+      <c r="H6" s="164"/>
+      <c r="I6" s="170"/>
+      <c r="J6" s="174"/>
+      <c r="K6" s="172"/>
+      <c r="L6" s="171"/>
+      <c r="M6" s="172"/>
+      <c r="N6" s="176"/>
       <c r="O6" s="21" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="P6" s="158"/>
+      <c r="P6" s="168"/>
       <c r="S6" s="15">
         <v>65160</v>
       </c>
@@ -3861,98 +3861,93 @@
       <c r="E19" s="18"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="D21" s="159" t="s">
+      <c r="D21" s="169" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="159"/>
-      <c r="F21" s="159"/>
-      <c r="G21" s="159"/>
-      <c r="H21" s="159"/>
-      <c r="I21" s="159"/>
-      <c r="J21" s="159"/>
-      <c r="K21" s="159"/>
-      <c r="L21" s="159"/>
-      <c r="M21" s="159"/>
-      <c r="N21" s="159"/>
-      <c r="O21" s="159"/>
+      <c r="E21" s="169"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="169"/>
+      <c r="H21" s="169"/>
+      <c r="I21" s="169"/>
+      <c r="J21" s="169"/>
+      <c r="K21" s="169"/>
+      <c r="L21" s="169"/>
+      <c r="M21" s="169"/>
+      <c r="N21" s="169"/>
+      <c r="O21" s="169"/>
     </row>
     <row r="22" spans="1:17">
-      <c r="D22" s="159"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="159"/>
-      <c r="G22" s="159"/>
-      <c r="H22" s="159"/>
-      <c r="I22" s="159"/>
-      <c r="J22" s="159"/>
-      <c r="K22" s="159"/>
-      <c r="L22" s="159"/>
-      <c r="M22" s="159"/>
-      <c r="N22" s="159"/>
-      <c r="O22" s="159"/>
+      <c r="D22" s="169"/>
+      <c r="E22" s="169"/>
+      <c r="F22" s="169"/>
+      <c r="G22" s="169"/>
+      <c r="H22" s="169"/>
+      <c r="I22" s="169"/>
+      <c r="J22" s="169"/>
+      <c r="K22" s="169"/>
+      <c r="L22" s="169"/>
+      <c r="M22" s="169"/>
+      <c r="N22" s="169"/>
+      <c r="O22" s="169"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="D23" s="159"/>
-      <c r="E23" s="159"/>
-      <c r="F23" s="159"/>
-      <c r="G23" s="159"/>
-      <c r="H23" s="159"/>
-      <c r="I23" s="159"/>
-      <c r="J23" s="159"/>
-      <c r="K23" s="159"/>
-      <c r="L23" s="159"/>
-      <c r="M23" s="159"/>
-      <c r="N23" s="159"/>
-      <c r="O23" s="159"/>
+      <c r="D23" s="169"/>
+      <c r="E23" s="169"/>
+      <c r="F23" s="169"/>
+      <c r="G23" s="169"/>
+      <c r="H23" s="169"/>
+      <c r="I23" s="169"/>
+      <c r="J23" s="169"/>
+      <c r="K23" s="169"/>
+      <c r="L23" s="169"/>
+      <c r="M23" s="169"/>
+      <c r="N23" s="169"/>
+      <c r="O23" s="169"/>
     </row>
     <row r="24" spans="1:17">
-      <c r="D24" s="159"/>
-      <c r="E24" s="159"/>
-      <c r="F24" s="159"/>
-      <c r="G24" s="159"/>
-      <c r="H24" s="159"/>
-      <c r="I24" s="159"/>
-      <c r="J24" s="159"/>
-      <c r="K24" s="159"/>
-      <c r="L24" s="159"/>
-      <c r="M24" s="159"/>
-      <c r="N24" s="159"/>
-      <c r="O24" s="159"/>
+      <c r="D24" s="169"/>
+      <c r="E24" s="169"/>
+      <c r="F24" s="169"/>
+      <c r="G24" s="169"/>
+      <c r="H24" s="169"/>
+      <c r="I24" s="169"/>
+      <c r="J24" s="169"/>
+      <c r="K24" s="169"/>
+      <c r="L24" s="169"/>
+      <c r="M24" s="169"/>
+      <c r="N24" s="169"/>
+      <c r="O24" s="169"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="D25" s="159"/>
-      <c r="E25" s="159"/>
-      <c r="F25" s="159"/>
-      <c r="G25" s="159"/>
-      <c r="H25" s="159"/>
-      <c r="I25" s="159"/>
-      <c r="J25" s="159"/>
-      <c r="K25" s="159"/>
-      <c r="L25" s="159"/>
-      <c r="M25" s="159"/>
-      <c r="N25" s="159"/>
-      <c r="O25" s="159"/>
+      <c r="D25" s="169"/>
+      <c r="E25" s="169"/>
+      <c r="F25" s="169"/>
+      <c r="G25" s="169"/>
+      <c r="H25" s="169"/>
+      <c r="I25" s="169"/>
+      <c r="J25" s="169"/>
+      <c r="K25" s="169"/>
+      <c r="L25" s="169"/>
+      <c r="M25" s="169"/>
+      <c r="N25" s="169"/>
+      <c r="O25" s="169"/>
     </row>
     <row r="26" spans="1:17" ht="65.25" customHeight="1">
-      <c r="D26" s="159"/>
-      <c r="E26" s="159"/>
-      <c r="F26" s="159"/>
-      <c r="G26" s="159"/>
-      <c r="H26" s="159"/>
-      <c r="I26" s="159"/>
-      <c r="J26" s="159"/>
-      <c r="K26" s="159"/>
-      <c r="L26" s="159"/>
-      <c r="M26" s="159"/>
-      <c r="N26" s="159"/>
-      <c r="O26" s="159"/>
+      <c r="D26" s="169"/>
+      <c r="E26" s="169"/>
+      <c r="F26" s="169"/>
+      <c r="G26" s="169"/>
+      <c r="H26" s="169"/>
+      <c r="I26" s="169"/>
+      <c r="J26" s="169"/>
+      <c r="K26" s="169"/>
+      <c r="L26" s="169"/>
+      <c r="M26" s="169"/>
+      <c r="N26" s="169"/>
+      <c r="O26" s="169"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D21:O26"/>
@@ -3966,6 +3961,11 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
